--- a/question_bank/BENGALI.xlsx
+++ b/question_bank/BENGALI.xlsx
@@ -9,24 +9,29 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="সমার্থক শব্দ" sheetId="7" r:id="rId1"/>
-    <sheet name="পদান্তর" sheetId="8" r:id="rId2"/>
-    <sheet name="এক কথায় প্রকাশ (Guide)" sheetId="9" r:id="rId3"/>
-    <sheet name="এক কথায় প্রকাশ" sheetId="3" r:id="rId4"/>
-    <sheet name="স্বরসন্ধি" sheetId="5" r:id="rId5"/>
-    <sheet name="ব‍্যঞ্জনসন্ধি" sheetId="6" r:id="rId6"/>
-    <sheet name="বিসর্গ সন্ধি" sheetId="4" r:id="rId7"/>
+    <sheet name="Syllabus" sheetId="12" r:id="rId1"/>
+    <sheet name="অর্থ ও বাক্য রচনা" sheetId="10" r:id="rId2"/>
+    <sheet name="বিপরীতার্থক শব্দ" sheetId="14" r:id="rId3"/>
+    <sheet name="সমার্থক শব্দ" sheetId="7" r:id="rId4"/>
+    <sheet name="পদান্তর" sheetId="8" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="13" r:id="rId6"/>
+    <sheet name="এক কথায় প্রকাশ (Guide)" sheetId="9" r:id="rId7"/>
+    <sheet name="এক কথায় প্রকাশ" sheetId="3" r:id="rId8"/>
+    <sheet name="স্বরসন্ধি" sheetId="5" r:id="rId9"/>
+    <sheet name="ব‍্যঞ্জনসন্ধি" sheetId="6" r:id="rId10"/>
+    <sheet name="বিসর্গ সন্ধি" sheetId="4" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'এক কথায় প্রকাশ'!$A$1:$B$932</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">পদান্তর!$A$1:$B$565</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'বিসর্গ সন্ধি'!$A$1:$B$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ব‍্যঞ্জনসন্ধি!$A$1:$B$144</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'সমার্থক শব্দ'!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">স্বরসন্ধি!$B$1:$B$348</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'অর্থ ও বাক্য রচনা'!$A$1:$C$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'এক কথায় প্রকাশ'!$A$1:$B$932</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">পদান্তর!$A$1:$B$565</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'বিসর্গ সন্ধি'!$A$1:$B$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">ব‍্যঞ্জনসন্ধি!$A$1:$B$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'সমার্থক শব্দ'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">স্বরসন্ধি!$B$1:$B$348</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4548" uniqueCount="4399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5154" uniqueCount="4943">
   <si>
     <t>বাগীশ</t>
   </si>
@@ -16121,9 +16126,6 @@
     <t>অগম্য</t>
   </si>
   <si>
-    <t>Questions</t>
-  </si>
-  <si>
     <t>Answers</t>
   </si>
   <si>
@@ -23006,13 +23008,1648 @@
   </si>
   <si>
     <t>বাক্‌রূদ্ধ</t>
+  </si>
+  <si>
+    <t>অনুতাপ</t>
+  </si>
+  <si>
+    <t>অবারিত</t>
+  </si>
+  <si>
+    <t>অবিস্মরণীয়</t>
+  </si>
+  <si>
+    <t>আকাঙ্ক্ষা</t>
+  </si>
+  <si>
+    <t>আতিথেয়তা</t>
+  </si>
+  <si>
+    <t>উদারতা</t>
+  </si>
+  <si>
+    <t>উদ্যোগ</t>
+  </si>
+  <si>
+    <t>উন্নতি</t>
+  </si>
+  <si>
+    <t>কৌতূহল</t>
+  </si>
+  <si>
+    <t>কৃতজ্ঞতা</t>
+  </si>
+  <si>
+    <t>ক্ষিপ্রতা</t>
+  </si>
+  <si>
+    <t>গাম্ভীর্য</t>
+  </si>
+  <si>
+    <t>চমকপ্রদ</t>
+  </si>
+  <si>
+    <t>তৎপরতা</t>
+  </si>
+  <si>
+    <t>তিমির</t>
+  </si>
+  <si>
+    <t>তীব্রতা</t>
+  </si>
+  <si>
+    <t>দুরন্ত</t>
+  </si>
+  <si>
+    <t>দুঃসাহস</t>
+  </si>
+  <si>
+    <t>দূরদর্শিতা</t>
+  </si>
+  <si>
+    <t>নমনীয়</t>
+  </si>
+  <si>
+    <t>নিরহংকার</t>
+  </si>
+  <si>
+    <t>নিবিড়</t>
+  </si>
+  <si>
+    <t>পরিশ্রমী</t>
+  </si>
+  <si>
+    <t>প্রতিশ্রুতি</t>
+  </si>
+  <si>
+    <t>প্রতিভা</t>
+  </si>
+  <si>
+    <t>প্রবল</t>
+  </si>
+  <si>
+    <t>প্রশান্তি</t>
+  </si>
+  <si>
+    <t>বিচক্ষণ</t>
+  </si>
+  <si>
+    <t>বিস্ময়</t>
+  </si>
+  <si>
+    <t>বিলাসবহুল</t>
+  </si>
+  <si>
+    <t>বিচিত্র</t>
+  </si>
+  <si>
+    <t>মনোমুগ্ধকর</t>
+  </si>
+  <si>
+    <t>মনোযোগ</t>
+  </si>
+  <si>
+    <t>মহৎ</t>
+  </si>
+  <si>
+    <t>মূল্যবান</t>
+  </si>
+  <si>
+    <t>যশ</t>
+  </si>
+  <si>
+    <t>রূপান্তর</t>
+  </si>
+  <si>
+    <t>শিষ্টাচার</t>
+  </si>
+  <si>
+    <t>সংকল্প</t>
+  </si>
+  <si>
+    <t>সতর্কতা</t>
+  </si>
+  <si>
+    <t>সমৃদ্ধি</t>
+  </si>
+  <si>
+    <t>সহযোগিতা</t>
+  </si>
+  <si>
+    <t>সুনাম</t>
+  </si>
+  <si>
+    <t>সৃষ্টিশীল</t>
+  </si>
+  <si>
+    <t>স্বাবলম্বী</t>
+  </si>
+  <si>
+    <t>অক্লান্ত</t>
+  </si>
+  <si>
+    <t>অগ্রাধিকার</t>
+  </si>
+  <si>
+    <t>অনন্য</t>
+  </si>
+  <si>
+    <t>অনুসন্ধান</t>
+  </si>
+  <si>
+    <t>অপরাজিত</t>
+  </si>
+  <si>
+    <t>অভিমুখে</t>
+  </si>
+  <si>
+    <t>অভিযান</t>
+  </si>
+  <si>
+    <t>আকর্ষণীয়</t>
+  </si>
+  <si>
+    <t>আলোকপাত</t>
+  </si>
+  <si>
+    <t>উজ্জ্বলতা</t>
+  </si>
+  <si>
+    <t>উৎসর্গ</t>
+  </si>
+  <si>
+    <t>ঐতিহ্য</t>
+  </si>
+  <si>
+    <t>কলকাকলি</t>
+  </si>
+  <si>
+    <t>কল্পনাপ্রসূত</t>
+  </si>
+  <si>
+    <t>কীর্তি</t>
+  </si>
+  <si>
+    <t>গতিশীল</t>
+  </si>
+  <si>
+    <t>গবেষণা</t>
+  </si>
+  <si>
+    <t>গৌরবময়</t>
+  </si>
+  <si>
+    <t>জাতীয়তাবাদ</t>
+  </si>
+  <si>
+    <t>তদারকি</t>
+  </si>
+  <si>
+    <t>তীরবর্তী</t>
+  </si>
+  <si>
+    <t>দূরতিক্রম্য</t>
+  </si>
+  <si>
+    <t>দৃষ্টিভঙ্গি</t>
+  </si>
+  <si>
+    <t>দেশপ্রেম</t>
+  </si>
+  <si>
+    <t>নৈপুণ্য</t>
+  </si>
+  <si>
+    <t>পথপ্রদর্শক</t>
+  </si>
+  <si>
+    <t>পরিবেশবান্ধব</t>
+  </si>
+  <si>
+    <t>পরিকল্পনা</t>
+  </si>
+  <si>
+    <t>পরিবর্তনশীল</t>
+  </si>
+  <si>
+    <t>প্রতিযোগিতা</t>
+  </si>
+  <si>
+    <t>প্রতিবাদী</t>
+  </si>
+  <si>
+    <t>প্রতিধ্বনিত</t>
+  </si>
+  <si>
+    <t>প্রেরণা</t>
+  </si>
+  <si>
+    <t>বজ্রকণ্ঠ</t>
+  </si>
+  <si>
+    <t>বাস্তবধর্মী</t>
+  </si>
+  <si>
+    <t>বিস্ময়কর</t>
+  </si>
+  <si>
+    <t>ব্যতিক্রম</t>
+  </si>
+  <si>
+    <t>শৃঙ্খলাপরায়ণ</t>
+  </si>
+  <si>
+    <t>সংবেদনশীল</t>
+  </si>
+  <si>
+    <t>সুদূরপ্রসারী</t>
+  </si>
+  <si>
+    <t>স্বতঃস্ফূর্ত</t>
+  </si>
+  <si>
+    <t>অপ্রত্যাশিত</t>
+  </si>
+  <si>
+    <t>অনুকরণীয়</t>
+  </si>
+  <si>
+    <t>অন্তর্নিহিত</t>
+  </si>
+  <si>
+    <t>অভিভূত</t>
+  </si>
+  <si>
+    <t>আত্মবিশ্বাসী</t>
+  </si>
+  <si>
+    <t>আবির্ভাব</t>
+  </si>
+  <si>
+    <t>আশাতীত</t>
+  </si>
+  <si>
+    <t>ইতস্তত</t>
+  </si>
+  <si>
+    <t>উদারচেতা</t>
+  </si>
+  <si>
+    <t>একাত্মতা</t>
+  </si>
+  <si>
+    <t>ঐতিহাসিকতা</t>
+  </si>
+  <si>
+    <t>ক্ষণস্থায়ী</t>
+  </si>
+  <si>
+    <t>খ্যাতনামা</t>
+  </si>
+  <si>
+    <t>জনকল্যাণ</t>
+  </si>
+  <si>
+    <t>জ্ঞানপিপাসা</t>
+  </si>
+  <si>
+    <t>তিলধারণ</t>
+  </si>
+  <si>
+    <t>দুরতিক্রম্য</t>
+  </si>
+  <si>
+    <t>দূরপাল্লা</t>
+  </si>
+  <si>
+    <t>দৃঢ়তা</t>
+  </si>
+  <si>
+    <t>দূরভিসন্ধি</t>
+  </si>
+  <si>
+    <t>দেশাত্মবোধ</t>
+  </si>
+  <si>
+    <t>নজরকাড়া</t>
+  </si>
+  <si>
+    <t>নান্দনিক</t>
+  </si>
+  <si>
+    <t>নিয়মানুবর্তিতা</t>
+  </si>
+  <si>
+    <t>নিষ্কলঙ্ক</t>
+  </si>
+  <si>
+    <t>পর্যবেক্ষণ</t>
+  </si>
+  <si>
+    <t>পুনরুত্থান</t>
+  </si>
+  <si>
+    <t>প্রতিযোগিতামূলক</t>
+  </si>
+  <si>
+    <t>প্রেরণাদায়ক</t>
+  </si>
+  <si>
+    <t>বহুমাত্রিক</t>
+  </si>
+  <si>
+    <t>বাগ্মিতা</t>
+  </si>
+  <si>
+    <t>বাস্তবসম্মত</t>
+  </si>
+  <si>
+    <t>বিচারবুদ্ধি</t>
+  </si>
+  <si>
+    <t>বিস্ময়বিমুগ্ধ</t>
+  </si>
+  <si>
+    <t>মননশীলতা</t>
+  </si>
+  <si>
+    <t>যুগান্তকারী</t>
+  </si>
+  <si>
+    <t>লড়াকু</t>
+  </si>
+  <si>
+    <t>শৈল্পিক</t>
+  </si>
+  <si>
+    <t>সততা</t>
+  </si>
+  <si>
+    <t>সুদূরপরাহত</t>
+  </si>
+  <si>
+    <t>অকুণ্ঠ</t>
+  </si>
+  <si>
+    <t>অঙ্গীকার</t>
+  </si>
+  <si>
+    <t>অনভিজ্ঞ</t>
+  </si>
+  <si>
+    <t>অনুশাসন</t>
+  </si>
+  <si>
+    <t>অন্তরীক্ষ</t>
+  </si>
+  <si>
+    <t>অপচয়</t>
+  </si>
+  <si>
+    <t>অপ্রতিরোধ্য</t>
+  </si>
+  <si>
+    <t>অভিজ্ঞতা</t>
+  </si>
+  <si>
+    <t>অভ্যর্থনা</t>
+  </si>
+  <si>
+    <t>আমূল</t>
+  </si>
+  <si>
+    <t>আশঙ্কাজনক</t>
+  </si>
+  <si>
+    <t>আশ্লিষ্ট</t>
+  </si>
+  <si>
+    <t>উত্তরণ</t>
+  </si>
+  <si>
+    <t>উৎসুক</t>
+  </si>
+  <si>
+    <t>ঐকান্তিক</t>
+  </si>
+  <si>
+    <t>ঐক্যবদ্ধ</t>
+  </si>
+  <si>
+    <t>কঠোরতা</t>
+  </si>
+  <si>
+    <t>কৃতিত্ব</t>
+  </si>
+  <si>
+    <t>গগনচুম্বী</t>
+  </si>
+  <si>
+    <t>ঘনঘটা</t>
+  </si>
+  <si>
+    <t>জনপ্রিয়তা</t>
+  </si>
+  <si>
+    <t>তাত্পর্যপূর্ণ</t>
+  </si>
+  <si>
+    <t>দূরদৃষ্টি</t>
+  </si>
+  <si>
+    <t>ধূমকেতু</t>
+  </si>
+  <si>
+    <t>নিত্যপ্রয়োজনীয়</t>
+  </si>
+  <si>
+    <t>পরনির্ভরশীল</t>
+  </si>
+  <si>
+    <t>পরাস্ত</t>
+  </si>
+  <si>
+    <t>প্রাণবন্ত</t>
+  </si>
+  <si>
+    <t>বিবেকবান</t>
+  </si>
+  <si>
+    <t>বৈচিত্র্যময়</t>
+  </si>
+  <si>
+    <t>বৈজ্ঞানিক</t>
+  </si>
+  <si>
+    <t>ব্যস্ততা</t>
+  </si>
+  <si>
+    <t>মহীয়সী</t>
+  </si>
+  <si>
+    <t>রক্ষণাবেক্ষণ</t>
+  </si>
+  <si>
+    <t>লজ্জাজনক</t>
+  </si>
+  <si>
+    <t>শিক্ষণীয়</t>
+  </si>
+  <si>
+    <t>শোভাময়</t>
+  </si>
+  <si>
+    <t>শ্রদ্ধাঞ্জলি</t>
+  </si>
+  <si>
+    <t>সার্বভৌম</t>
+  </si>
+  <si>
+    <t>স্বচ্ছতা</t>
+  </si>
+  <si>
+    <t>অর্থ (Meaning) || বাক্য গঠন (Sentence)</t>
+  </si>
+  <si>
+    <t>আফসোস / পস্তানি (Remorse) || ভুল কাজটি করার পর তার মনে অনুতাপ হলো।</t>
+  </si>
+  <si>
+    <t>উন্মুক্ত / খোলা (Unrestricted) || জানলা দিয়ে অবারিত বাতাস ঘরে আসছে।</t>
+  </si>
+  <si>
+    <t>যা ভোলা যায় না (Unforgettable) || আমাদের সুন্দরবনের ভ্রমণটি ছিল সত্যিই অবিস্মরণীয়।</t>
+  </si>
+  <si>
+    <t>আচমকা / হঠাৎ (Sudden) || আকস্মিক ঝড়ে বাগানের অনেক গাছ ভেঙে গেল।</t>
+  </si>
+  <si>
+    <t>তীব্র ইচ্ছা (Desire / Wish) || জীবনে বড় মানুষ হওয়ার আকাঙ্ক্ষা সবারই থাকে।</t>
+  </si>
+  <si>
+    <t>অতিথি সৎকার (Hospitality) || গ্রাম্য মানুষের আতিথেয়তা মন ছুঁয়ে যায়।</t>
+  </si>
+  <si>
+    <t>মহত্ব / দয়া (Generosity) || বিদ্যাসাগরের উদারতার কথা আমরা সবাই জানি।</t>
+  </si>
+  <si>
+    <t>চেষ্টা / আয়োজন (Initiative) || রবিন পাড়া পরিষ্কার করার জন্য একটি ভালো উদ্যোগ নিয়েছে।</t>
+  </si>
+  <si>
+    <t>প্রগতি / বৃদ্ধি (Improvement / Progress) || প্রতিদিন পড়াশোনা করলে তোমার পরীক্ষার ফলাফলের উন্নতি হবে।</t>
+  </si>
+  <si>
+    <t>জানার ইচ্ছা (Curiosity) || মহাকাশ নিয়ে ছোটদের মনে অনেক কৌতূহল থাকে।</t>
+  </si>
+  <si>
+    <t>উপকারীর উপকার স্বীকার করা (Gratitude) || শিক্ষকের সাহায্যের জন্য রাহুল তাঁর প্রতি কৃতজ্ঞতা প্রকাশ করল।</t>
+  </si>
+  <si>
+    <t>দ্রুততা (Agility / Swiftness) || চিতা বাঘ খুব ক্ষিপ্রতার সাথে শিকার ধরে।</t>
+  </si>
+  <si>
+    <t>ধীরস্থির ভাব (Gravity / Solemnity) || প্রধান শিক্ষকের কথার মধ্যে একটা গাম্ভীর্য আছে।</t>
+  </si>
+  <si>
+    <t>বিস্ময়কর (Astonishing) || জাদুকর মঞ্চে একটি চমকপ্রদ খেলা দেখালেন।</t>
+  </si>
+  <si>
+    <t>প্রশ্ন করার ইচ্ছা (Inquiry) || অজানা বিষয়ে শিক্ষকের কাছে সর্বদা জিজ্ঞাসা করা উচিত।</t>
+  </si>
+  <si>
+    <t>চটপটে ভাব (Promptness) || ফায়ার ব্রিগেডের তৎপরতায় আগুন দ্রুত নিয়ন্ত্রণে এল।</t>
+  </si>
+  <si>
+    <t>অন্ধকার (Darkness) || সকালের সূর্য উদয় হতেই রাতের তিমির কেটে গেল।</t>
+  </si>
+  <si>
+    <t>প্রচণ্ডতা (Intensity) || দুপুরের দিকে রোদের তীব্রতা অনেক বেড়ে যায়।</t>
+  </si>
+  <si>
+    <t>চঞ্চল / শান্ত নয় যে (Restless / Wild) || নীলিমা খুব দুরন্ত হলেও পড়াশোনায় বেশ ভালো।</t>
+  </si>
+  <si>
+    <t>অতিরিক্ত সাহস (Audacity / Reckless courage) || গভীর জঙ্গলে একা যাওয়ার মতো দুঃসাহস করো না।</t>
+  </si>
+  <si>
+    <t>ভবিষ্যতের কথা ভাবার ক্ষমতা (Foresight) || রাজার দূরদর্শিতার কারণে রাজ্যটি বড় বিপদ থেকে বেঁচে গেল।</t>
+  </si>
+  <si>
+    <t>সহনশীলতা (Patience) || কঠিন সময়ে আমাদের মনের ধৈর্য হারানো উচিত নয়।</t>
+  </si>
+  <si>
+    <t>নরম / নমনযোগ্য (Flexible) || সোনা একটি অত্যন্ত নমনীয় ধাতু।</t>
+  </si>
+  <si>
+    <t>যার অহংকার নেই (Humble) || বিজ্ঞানী জগদীশচন্দ্র বসু অত্যন্ত নিরহংকার মানুষ ছিলেন।</t>
+  </si>
+  <si>
+    <t>গভীর / ঘন (Dense / Intimate) || সুন্দরবনে নিবিড় অরণ্য দেখতে পাওয়া যায়।</t>
+  </si>
+  <si>
+    <t>যে খুব খাটে (Hardworking) || পরিশ্রমী ছাত্রছাত্রীরা জীবনে অবশ্যই সফল হয়।</t>
+  </si>
+  <si>
+    <t>কথা দেওয়া (Promise) || কোনো প্রতিশ্রুতি দিলে তা সব সময় রক্ষা করা উচিত।</t>
+  </si>
+  <si>
+    <t>সহজাত বুদ্ধি বা গুণ (Talent) || ছোটবেলা থেকেই সুকান্তর মধ্যে কবি প্রতিভা দেখা গিয়েছিল।</t>
+  </si>
+  <si>
+    <t>স্থাপন করা (Establishment) || ১৮১৬ সালে হিন্দু কলেজ প্রতিষ্ঠা করা হয়।</t>
+  </si>
+  <si>
+    <t>খুব জোরালো (Strong / Powerful) || কাল রাতে প্রবল ঝড়-বৃষ্টি হয়েছিল।</t>
+  </si>
+  <si>
+    <t>পরম শান্তি (Tranquility) || পাহাড়ি পরিবেশ মনের মধ্যে এক অপূর্ব প্রশান্তি আনে।</t>
+  </si>
+  <si>
+    <t>বুদ্ধিমান / দূরদর্শী (Wise / Prudent) || বীরবল ছিলেন আকবরের একজন অত্যন্ত বিচক্ষণ মন্ত্রী।</t>
+  </si>
+  <si>
+    <t>অবাক হওয়া (Wonder / Amazement) || জাদুকরের কাণ্ড দেখে দর্শকেরা বিস্ময় প্রকাশ করলেন।</t>
+  </si>
+  <si>
+    <t>আরামদায়ক ও দামি (Luxurious) || প্রাচীনকালে রাজারা বিলাসবহুল প্রাসাদে বাস করতেন।</t>
+  </si>
+  <si>
+    <t>নানান রকমের (Diverse / Varied) || আমাদের এই পৃথিবী নানা বিচিত্র জীবজন্তুতে ভরা।</t>
+  </si>
+  <si>
+    <t>মন কেড়ে নেয় এমন (Charming) || পাহাড়ের উপর থেকে সূর্যোদয়ের দৃশ্যটি অত্যন্ত মনোমুগ্ধকর।</t>
+  </si>
+  <si>
+    <t>একাগ্রতা (Attention) || ক্লাসে শিক্ষকের কথা সব সময় মনোযোগ দিয়ে শোনা উচিত।</t>
+  </si>
+  <si>
+    <t>উদার হৃদয়ের (Noble) || গরিব মানুষকে সাহায্য করা একটি অত্যন্ত মহৎ কাজ।</t>
+  </si>
+  <si>
+    <t>দামি / দরকারী (Valuable) || সময় আমাদের জীবনের সবচেয়ে মূল্যবান সম্পদ।</t>
+  </si>
+  <si>
+    <t>খ্যাতি / সুনাম (Fame) || ভালো কাজের মাধ্যমেই মানুষ সমাজে যশ লাভ করে।</t>
+  </si>
+  <si>
+    <t>অন্য রূপে বদলানো (Transformation) || বিজ্ঞান ক্লাসে আমরা জলের বাষ্পে রূপান্তর হওয়া শিখলাম।</t>
+  </si>
+  <si>
+    <t>ভদ্র আচরণ (Etiquette / Politeness) || বড়দের সম্মান করা এবং ছোটদের ভালোবাসা অন্যতম প্রধান শিষ্টাচার।</t>
+  </si>
+  <si>
+    <t>সৌন্দর্য (Beauty / Grace) || বসন্তকালে গাছে গাছে ফুলের শোভা দেখার মতো হয়।</t>
+  </si>
+  <si>
+    <t>দৃঢ় প্রতিজ্ঞা (Determination) || পরীক্ষায় ভালো ফল করার জন্য সে মনে মনে সংকল্প করল।</t>
+  </si>
+  <si>
+    <t>সাবধানতা (Caution) || রাস্তা পার হওয়ার সময় আমাদের বিশেষ সতর্কতা অবলম্বন করতে হবে।</t>
+  </si>
+  <si>
+    <t>উন্নতি ও ঐশ্বর্য (Prosperity) || কৃষিকাজের উন্নতির ফলেই দেশের অর্থনৈতিক সমৃদ্ধি আসে।</t>
+  </si>
+  <si>
+    <t>একসঙ্গে কাজ করা (Cooperation) || সবার সহযোগিতা ছাড়া এই বড় অনুষ্ঠানটি সফল হতো না।</t>
+  </si>
+  <si>
+    <t>ভালো নাম / খ্যাতি (Reputation) || সততার কারণে বাজারে ওই দোকানদারের খুব সুনাম আছে।</t>
+  </si>
+  <si>
+    <t>নতুন কিছু তৈরি করার ক্ষমতাসম্পন্ন (Creative) || অঙ্কন প্রতিযোগিতায় শিশুরা তাদের সৃষ্টিশীল ভাবনার পরিচয় দিল।</t>
+  </si>
+  <si>
+    <t>নিজের ওপর নির্ভরশীল (Self-reliant) || পড়ালেখা শিখে নিজের পায়ে দাঁড়িয়ে স্বাবলম্বী হওয়া দরকার।</t>
+  </si>
+  <si>
+    <t>যা পরিশ্রমে ক্লান্ত হয় না (Untiring / Indefatigable) || বিজ্ঞানীদের অক্লান্ত পরিশ্রমে নতুন ওষুধটি আবিষ্কৃত হলো।</t>
+  </si>
+  <si>
+    <t>সবার আগে সুযোগ পাওয়া (Priority) || টিকিট কাউন্টারে বয়স্ক মানুষদের অগ্রাধিকার দেওয়া উচিত।</t>
+  </si>
+  <si>
+    <t>যার তুলনা নেই / অসাধারণ (Unique) || তাজমহলের স্থাপত্যশৈলী সত্যিই পৃথিবীর বুকে অনন্য।</t>
+  </si>
+  <si>
+    <t>উৎসাহ জোগানো (Inspiration) || স্বামী বিবেকানন্দের বাণী যুবসমাজকে এগিয়ে যাওয়ার অনুপ্রেরণা দেয়।</t>
+  </si>
+  <si>
+    <t>খোঁজাখুঁজি / তদন্ত (Investigation / Search) || পুলিশ নিখোঁজ ছেলেটির খোঁজে চারিদিকে অনুসন্ধান চালাচ্ছে।</t>
+  </si>
+  <si>
+    <t>যে কখনো হারেনি (Unbeaten / Undefeated) || আমাদের স্কুলের ফুটবল দলটি টুর্নামেন্টে এখনও অপরাজিত।</t>
+  </si>
+  <si>
+    <t>যা ছাড়া চলে না (Essential) || সুস্থ শরীরের জন্য প্রতিদিন সুষম আহার এবং জল অপরিহার্য।</t>
+  </si>
+  <si>
+    <t>কোনো একটি দিকে (Towards) || বিকেলের দিকে পরিযায়ী পাখিরা তাদের নীড়ের অভিমুখে উড়ে চলল।</t>
+  </si>
+  <si>
+    <t>নতুন বা কঠিন যাত্রা (Expedition / Mission) || এভারেস্ট জয় করার জন্য পর্বতারোহীদের দল একটি নতুন অভিযান শুরু করল।</t>
+  </si>
+  <si>
+    <t>যা মন টানে (Attractive) || মেলার মাঠে খেলনার দোকানটি খুব আকর্ষণীয় করে সাজানো হয়েছে।</t>
+  </si>
+  <si>
+    <t>আলো ফেলা / ব্যাখ্যা করা (Shed light on) || শিক্ষক মহাশয় আজ ক্লাসে ভারতের স্বাধীনতা সংগ্রামের ওপর আলোকপাত করলেন।</t>
+  </si>
+  <si>
+    <t>ভরসা দেওয়া (Assurance) || ডাক্তারবাবু রোগীকে দ্রুত সুস্থ হয়ে ওঠার আশ্বাস দিলেন।</t>
+  </si>
+  <si>
+    <t>দীপ্তি / আলোকময় ভাব (Brightness / Radiance) || অমাবস্যার রাতেও ধ্রুবতারার উজ্জ্বলতা চোখে পড়ার মতো ছিল।</t>
+  </si>
+  <si>
+    <t>কোনো উদ্দেশ্যে সঁপে দেওয়া (Dedication / Sacrifice) || দেশপ্রেমিকেরা দেশের স্বাধীনতার জন্য নিজেদের জীবন উৎসর্গ করেছিলেন।</t>
+  </si>
+  <si>
+    <t>ইতিহাস সংক্রান্ত / পুরোনো ও গুরুত্বপূর্ণ (Historical) || দিল্লির লালকেল্লা ভারতের একটি অত্যন্ত গুরুত্বপূর্ণ ঐতিহাসিক স্থান।</t>
+  </si>
+  <si>
+    <t>অতীত থেকে চলে আসা গৌরব (Tradition / Heritage) || দুর্গাপূজা বাংলার এক প্রাচীন এবং ঐতিহ্যবাহী ঐতিহ্য।</t>
+  </si>
+  <si>
+    <t>পাখিদের মিষ্টি কিচিরমিচির (Chirping of birds) || ভোরবেলা পাখিদের মিষ্টি কলকাকলিতে আমার ঘুম ভেঙে গেল।</t>
+  </si>
+  <si>
+    <t>মনগড়া বা কাল্পনিক (Imaginary / Fictional) || রূপকথার গল্পগুলো সাধারণত সম্পূর্ণ কল্পনাপ্রসূত হয়ে থাকে।</t>
+  </si>
+  <si>
+    <t>গৌরবময় কাজ / সাফল্য (Achievement / Deed) || নিজের মহৎ কীর্তির জন্যই ঈশ্বরচন্দ্র বিদ্যাসাগর আজও অমর হয়ে আছেন।</t>
+  </si>
+  <si>
+    <t>যা চলছে বা সচল (Dynamic / In motion) || বিজ্ঞান ও প্রযুক্তির অগ্রগতির কারণে বর্তমান সমাজ খুব গতিশীল।</t>
+  </si>
+  <si>
+    <t>কোনো বিষয়ে গভীর পড়াশোনা ও পরীক্ষা (Research) || নতুন কোনো গ্রহের সন্ধানে বিজ্ঞানীরা মহাকাশ নিয়ে গবেষণা করছেন।</t>
+  </si>
+  <si>
+    <t>অত্যন্ত সম্মানের (Glorious) || ভারতের ইতিহাসে মৌর্য বংশের রাজত্বকাল ছিল অত্যন্ত গৌরবময়।</t>
+  </si>
+  <si>
+    <t>লোকজনে ভরা / ভিড় (Crowded / Populous) || পুজোর সময়ে কলকাতার রাস্তাঘাটগুলো অত্যন্ত জনাকীর্ণ হয়ে পড়ে।</t>
+  </si>
+  <si>
+    <t>দেশের প্রতি গভীর ভালোবাসা (Nationalism) || নেতাজির ভাষণ দেশবাসীর মনে তীব্র জাতীয়তাবাদ জাগিয়ে তুলেছিল।</t>
+  </si>
+  <si>
+    <t>জয়ের তীব্র ইচ্ছা (Desire to win / Conquer) || প্রতিযোগীদের মনের ভেতরের জিগীষা খেলায় দারুণ উত্তেজনা তৈরি করল।</t>
+  </si>
+  <si>
+    <t>দেখাশোনা করা (Supervision) || বাবার অনুপস্থিতিতে দাদাই পুরো ব্যবসার কাজ তদারকি করে।</t>
+  </si>
+  <si>
+    <t>নদীর পাড়ে অবস্থিত (Riverside / Coastal) || গঙ্গার তীরবর্তী অঞ্চলগুলোর আবহাওয়া বেশ মনোরম হয়।</t>
+  </si>
+  <si>
+    <t>যেখানে আকাশ মাটিতে মিশেছে বলে মনে হয় (Horizon) || সমুদ্রের পাড়ে দাঁড়ালে অসীম দিগন্ত চোখ জুড়িয়ে দেয়।</t>
+  </si>
+  <si>
+    <t>যা সহজে পাওয়া যায় না (Rare) || লাইব্রেরিতে পুরোনো আমলের কিছু দুর্লভ বইয়ের সংগ্রহ আছে।</t>
+  </si>
+  <si>
+    <t>যা পার হওয়া খুব কঠিন (Difficult to cross) || দুর্গম হিমালয় পর্বত একসময় মানুষের কাছে দূরতিক্রম্য ছিল।</t>
+  </si>
+  <si>
+    <t>দেখার বা ভাবার কায়দা (Perspective / Outlook) || ইতিবাচক দৃষ্টিভঙ্গি রাখলে জীবনের প্রতিটা কঠিন কাজই সহজ মনে হয়।</t>
+  </si>
+  <si>
+    <t>দেশের প্রতি ভালোবাসা (Patriotism) || ক্ষুদিরাম বসুর বীরত্ব ও দেশপ্রেম আমাদের অনুপ্রাণিত করে।</t>
+  </si>
+  <si>
+    <t>কাজে বিশেষ দক্ষতা (Skill / Mastery) || তুলির টানে চিত্রশিল্পী তাঁর অসাধারণ চিত্রকর্মের নৈপুণ্য ফুটিয়ে তুললেন।</t>
+  </si>
+  <si>
+    <t>যে পথ দেখায় (Guide / Pioneer) || ঈশ্বরচন্দ্র বিদ্যাসাগর ছিলেন নারীশিক্ষার অন্যতম পথপ্রদর্শক।</t>
+  </si>
+  <si>
+    <t>যা পরিবেশের ক্ষতি করে না (Eco-friendly) || প্লাস্টিকের বদলে পাটের ব্যাগ ব্যবহার করা একটি পরিবেশবান্ধব অভ্যাস।</t>
+  </si>
+  <si>
+    <t>কোনো কাজ করার আগের ছক (Planning) || সঠিক পরিকল্পনা ছাড়া কোনো বড় কাজে সফল হওয়া কঠিন।</t>
+  </si>
+  <si>
+    <t>যা বারবার বদলায় (Changeable / Dynamic) || ফ্যাশনের দুনিয়া সব সময়ই খুব পরিবর্তনশীল হয়।</t>
+  </si>
+  <si>
+    <t>পাল্লা দেওয়া বা রেষারেষি (Competition) || বার্ষিক ক্রীড়া প্রতিযোগিতায় অংশ নেওয়ার জন্য সব ছাত্রই উত্তেজিত।</t>
+  </si>
+  <si>
+    <t>অন্যায়ের বিরুদ্ধে যে কথা বলে (Protesting) || সমাজের যেকোনো অন্যায়ের বিরুদ্ধে আমাদের প্রতিবাদী হওয়া উচিত।</t>
+  </si>
+  <si>
+    <t>শব্দ দেওয়ালে লেগে ফিরে আসা (Echoed) || পাহাড়ি গুহার ভেতর জোরে কথা বললে সেই আওয়াজ প্রতিধ্বনিত হয়।</t>
+  </si>
+  <si>
+    <t>মনকে জাগিয়ে তোলা বা উৎসাহ (Inspiration / Stimulus) || মায়ের মুখের মিষ্টি কথা পরীক্ষার আগে আমাকে দারুণ প্রেরণা দেয়।</t>
+  </si>
+  <si>
+    <t>মেঘের ডাকের মতো গম্ভীর গলার আওয়াজ (Thundering voice) || নেতার বজ্রকণ্ঠ শুনে জনসভার হাজার হাজার মানুষ শান্ত হয়ে গেল।</t>
+  </si>
+  <si>
+    <t>যা সত্য বা বাস্তবের কাছাকাছি (Realistic) || রূপকথা নয়, গল্পের বইতে আজকাল বাচ্চারা বাস্তবধর্মী গল্প পছন্দ করে।</t>
+  </si>
+  <si>
+    <t>যা অবাক করে দেয় (Wonderful / Marvelous) || বিজ্ঞান আমাদের প্রতিদিন নতুন নতুন বিস্ময়কর জিনিস উপহার দিচ্ছে।</t>
+  </si>
+  <si>
+    <t>নিয়মের বাইরের কিছু (Exception) || সব পাখি আকাশে উড়লেও উটপাখি এর একটি বড় ব্যতিক্রম।</t>
+  </si>
+  <si>
+    <t>যে নিয়ম মেনে চলে (Disciplined) || একজন শৃঙ্খলাপরায়ণ ছাত্র সবসময় সঠিক সময়ে তার সব কাজ শেষ করে।</t>
+  </si>
+  <si>
+    <t>পুরনো কুপ্রথা দূর করা বা বদলানো (Reform) || রাজা রামমোহন রায় সতীদাহ প্রথার মতো কুপ্রথার সংস্কার করেছিলেন।</t>
+  </si>
+  <si>
+    <t>অন্যের দুঃখ কষ্ট সহজে বোঝে যে (Sensitive) || কবি ও সাহিত্যিকেরা সাধারণত অত্যন্ত সংবেদনশীল মনের মানুষ হন।</t>
+  </si>
+  <si>
+    <t>যার ফল অনেক দূর পর্যন্ত যায় (Far-reaching) || শৈশবের ভালো অভ্যাসগুলোর প্রভাব মানুষের জীবনে সুদূরপ্রসারী হয়।</t>
+  </si>
+  <si>
+    <t>যা নিজে থেকেই প্রকাশ পায় (Spontaneous) || শিক্ষকের মজার গল্প শুনে ক্লাসের সব বাচ্চার মনে স্বতঃস্ফূর্ত হাসি ফুটে উঠল।</t>
+  </si>
+  <si>
+    <t>যা আশা করা যায়নি (Unexpected) || জন্মদিনে বন্ধুর কাছ থেকে উপহার পেয়ে আমার মনে অপ্রত্যাশিত আনন্দ হলো।</t>
+  </si>
+  <si>
+    <t>যাকে দমন করা যায় না (Indomitable) || অদম্য ইচ্ছাশক্তি থাকলে যেকোনো কঠিন কাজে জয়লাভ করা সম্ভব।</t>
+  </si>
+  <si>
+    <t>যা নকল বা অনুসরণ করার যোগ্য (Exemplary) || মনীষীদের জীবনচরিত্র সব সময়ই নতুন প্রজন্মের কাছে অনুকরণীয়।</t>
+  </si>
+  <si>
+    <t>ভেতরে লুকিয়ে থাকা (Inherent / Hidden) || শিক্ষার আসল উদ্দেশ্য হলো শিশুর অন্তর্নিহিত গুণের বিকাশ ঘটানো।</t>
+  </si>
+  <si>
+    <t>আপ্লুত / মুগ্ধ (Overwhelmed) || গায়কের মিষ্টি কণ্ঠের গান শুনে শ্রোতারা সম্পূর্ণ অভিভূত হয়ে গেলেন।</t>
+  </si>
+  <si>
+    <t>নিজের ওপর যার ভরসা আছে (Self-confident) || আত্মবিশ্বাসী মানুষ জীবনের কোনো বাধাকেই ভয় পায় না।</t>
+  </si>
+  <si>
+    <t>প্রকাশ পাওয়া / উদয় হওয়া (Advent / Appearance) || শরৎকালে আকাশে সাদা মেঘের ভেলা নিয়ে দুর্গোৎসবের আবির্ভাব ঘটে।</t>
+  </si>
+  <si>
+    <t>আশার চেয়েও বেশি (Beyond expectation) || কঠোর পরিশ্রমের ফলে এবার সে পরীক্ষায় আশাতীত নম্বর পেয়েছে।</t>
+  </si>
+  <si>
+    <t>দ্বিধাবোধ / হেঁচকি খাওয়া (Hesitation / Scattered) || সত্যি কথাটা শিক্ষকের কাছে বলতে রাহুল খানিকটা ইতস্তত করছিল।</t>
+  </si>
+  <si>
+    <t>ব্যাকুলতা / চরম উদ্বেগ (Anxiety / Suspense) || পরীক্ষার ফলাফল প্রকাশের ঠিক আগে মনে এক ধরণের উৎকণ্ঠা কাজ করে।</t>
+  </si>
+  <si>
+    <t>চরম উন্নতি বা শ্রেষ্ঠত্ব (Excellence) || নিয়মিত অনুশীলনের মাধ্যমেই হাতের লেখার উৎকর্ষ বৃদ্ধি পায়।</t>
+  </si>
+  <si>
+    <t>বড় মনের মানুষ (Broad-minded) || সেই উদারচেতা ধনী ব্যক্তিটি তাঁর সমস্ত সম্পত্তি অনাথ আশ্রমে দান করলেন।</t>
+  </si>
+  <si>
+    <t>এক হয়ে যাওয়ার ভাব (Solidarity / Oneness) || দেশের সংকটের সময়ে সব নাগরিকের মধ্যে এক অদ্ভুত একাত্মতা দেখা গেল।</t>
+  </si>
+  <si>
+    <t>ইতিহাসের সত্যতা (Historicity) || মহাকাব্যের গল্পের চেয়ে এই ঘটনার ঐতিহাসিকতা অনেক বেশি প্রমাণিত।</t>
+  </si>
+  <si>
+    <t>যা অল্প সময় থাকে (Transient / Short-lived) || বৃষ্টির পর আকাশের রামধনু দেখতে খুব সুন্দর হলেও তা অত্যন্ত ক্ষণস্থায়ী।</t>
+  </si>
+  <si>
+    <t>খুব নামী বা বিখ্যাত (Famous / Renowned) || ডক্টর সর্বপল্লী রাধাকৃষ্ণন ছিলেন ভারতের একজন খ্যাতনামা শিক্ষক।</t>
+  </si>
+  <si>
+    <t>যা চিরকাল মনে রাখার মতো (Memorable forever) || স্বাধীনতা সংগ্রামীদের আত্মত্যাগ ইতিহাসে চিরস্মরণীয় হয়ে থাকবে।</t>
+  </si>
+  <si>
+    <t>মানুষের ভালো করা (Public welfare) || সরকার গ্রামীণ অঞ্চলে পানীয় জলের সুব্যবস্থা করে জনকল্যাণমূলক কাজ করেছে।</t>
+  </si>
+  <si>
+    <t>এই পৃথিবীর বা সংসারের (Earthly / Worldly) || সমস্ত জাগতিক সুখের চেয়ে মনের শান্তিতে থাকা অনেক বড় ব্যাপার।</t>
+  </si>
+  <si>
+    <t>জানার তীব্র ব্যাকুলতা (Thirst for knowledge) || লাইব্রেরির শান্ত পরিবেশে গেলে মানুষের জ্ঞানপিপাসা আরও বেড়ে যায়।</t>
+  </si>
+  <si>
+    <t>ঋষিদের আশ্রম (Hermitage) || প্রাচীনকালে শিক্ষার্থীরা শিক্ষার্জনের জন্য গুরুগৃহ বা তপোবন-এ বাস করত।</t>
+  </si>
+  <si>
+    <t>তিল রাখার মতো সামান্য জায়গা (A tiny space) || পুজোর দিনে মণ্ডপের ভেতরে তিলধারণ করার মতোও জায়গা ছিল না।</t>
+  </si>
+  <si>
+    <t>যা পার হওয়া কঠিন (Insurmountable) || সমস্ত দুরতিক্রম্য বাধা পেরিয়ে অভিযাত্রীরা অবশেষে পর্বতশৃঙ্গে পৌঁছালেন।</t>
+  </si>
+  <si>
+    <t>অনেক দূরের পথ (Long-distance) || আমরা গরমের ছুটিতে ভ্রমণের জন্য একটি দূরপাল্লার ট্রেনে চড়ে বসলাম।</t>
+  </si>
+  <si>
+    <t>শক্ত ভাব বা একগুঁয়েমি (Firmness / Resolve) || অধিনায়কের মানসিক দৃঢ়তার কারণেই শেষ মুহূর্তে আমরা ম্যাচটি জিতলাম।</t>
+  </si>
+  <si>
+    <t>খারাপ কোনো মতলব (Evil design / Ulterior motive) || শত্রু সৈন্যের দূরভিসন্ধির কথা টের পেয়েই সেনাপতি পাহারা বাড়িয়ে দিলেন।</t>
+  </si>
+  <si>
+    <t>দেশের প্রতি গভীর ভক্তি ও টান (Patriotism) || প্রজাতন্ত্র দিবসের প্যারেড দেখলে সবার মনে দেশাত্মবোধ জাগ্রত হয়।</t>
+  </si>
+  <si>
+    <t>যা সহজেই চোখ টানে (Eye-catching) || বিজ্ঞান প্রদর্শনীতে আমাদের স্কুলের তৈরি মডেলটি ছিল বেশ নজরকাড়া।</t>
+  </si>
+  <si>
+    <t>সৌন্দর্য বিষয়ক / শিল্পসম্মত (Aesthetic) || মাটির তৈরি পুতুলগুলোর মধ্যে এক অপূর্ব নান্দনিক ছোঁয়া রয়েছে।</t>
+  </si>
+  <si>
+    <t>নিয়ম মেনে চলার অভ্যাস (Regularity / Discipline) || সফল জীবনের মূল চাবিকাঠি হলো সময়ের সঠিক ব্যবহার ও নিয়মানুবর্তিতা।</t>
+  </si>
+  <si>
+    <t>যাতে কোনো দাগ বা খামতি নেই (Spotless / Pure) || শরৎকালের মেঘমুক্ত নিষ্কলঙ্ক চাঁদের আলো দেখতে ভারী চমৎকার লাগে।</t>
+  </si>
+  <si>
+    <t>অন্যের ভালো করা (Altruism / Helping others) || নিজের স্বার্থ ত্যাগ করে পরোপকার করার মধ্যেই প্রকৃত আনন্দ লুকিয়ে থাকে।</t>
+  </si>
+  <si>
+    <t>খুঁটিয়ে বা মন দিয়ে দেখা (Observation) || ল্যাবরেটরিতে বসে ছাত্ররা রাসায়নিক বিক্রিয়াটি গভীরভাবে পর্যবেক্ষণ করছে।</t>
+  </si>
+  <si>
+    <t>আবার জেগে ওঠা (Resurgence / Revival) || শীতকালের রুক্ষতা কাটিয়ে বসন্তে যেন প্রকৃতির এক নতুন পুনরুত্থান ঘটে।</t>
+  </si>
+  <si>
+    <t>প্রাচীন ইতিহাস ও মাটির নিচের বস্তু বিষয়ক (Archaeological) || সিন্ধু সভ্যতার শহরগুলো আবিষ্কারের পেছনে প্রত্নতাত্ত্বিক খননকার্যের বড় ভূমিকা ছিল।</t>
+  </si>
+  <si>
+    <t>পাল্লা দেওয়ার মতো পরিবেশ (Competitive) || আজকের এই প্রতিযোগিতামূলক যুগে টিকে থাকতে হলে নিয়মিত পড়াশোনা আবশ্যক।</t>
+  </si>
+  <si>
+    <t>তক্ষুনি বুদ্ধি খাটিয়ে কাজ করার ক্ষমতা (Presence of mind) || বীরবলের প্রত্যুৎপন্নমতিত্ব দেখে সম্রাট আকবর প্রায়ই পুরস্কার দিতেন।</t>
+  </si>
+  <si>
+    <t>যা উৎসাহ দেয় (Inspirational) || মহাপুরুষদের জীবনীমূলক গল্পগুলো শিশুদের জন্য অত্যন্ত প্রেরণাদায়ক।</t>
+  </si>
+  <si>
+    <t>যার অনেকগুলো দিক আছে (Multidimensional) || রবীন্দ্রনাথ ঠাকুর ছিলেন একজন অসাধারণ এবং বহুমাত্রিক প্রতিভার অধিকারী।</t>
+  </si>
+  <si>
+    <t>সুন্দর ও গুছিয়ে কথা বলার ক্ষমতা (Eloquence) || বিতর্ক প্রতিযোগিতায় অনন্যার অসাধারণ বাগ্মিতা বিচারকদের মুগ্ধ করল।</t>
+  </si>
+  <si>
+    <t>যা করা সম্ভব বা যুক্তিযুক্ত (Practical / Feasible) || কোনো কাজে হাত দেওয়ার আগে একটি বাস্তবসম্মত পরিকল্পনা করা দরকার।</t>
+  </si>
+  <si>
+    <t>ভালো-মন্দ বোঝার ক্ষমতা (Judgement / Common sense) || নিজের বিচারবুদ্ধি খাটিয়ে চললে ঠকে যাওয়ার সম্ভাবনা কম থাকে।</t>
+  </si>
+  <si>
+    <t>অবাক ও মোহিত হওয়া (Spellbound) || জাদুকরের শূন্যে ভেসে থাকার কৌশল দেখে দর্শকেরা বিস্ময়বিমুগ্ধ হয়ে রইলেন।</t>
+  </si>
+  <si>
+    <t>চিন্তাশক্তি বা বুদ্ধিমত্তা (Intellectuality / Thoughtfulness) || ভালো ভালো বই পড়ার অভ্যাস মানুষের মনের মননশীলতা বৃদ্ধি করে।</t>
+  </si>
+  <si>
+    <t>নতুন যুগের সূচনা করে যা (Revolutionary / Epoch-making) || পেনিসিলিন আবিষ্কার চিকিৎসা বিজ্ঞানের ইতিহাসে একটি যুগান্তকারী ঘটনা।</t>
+  </si>
+  <si>
+    <t>যে সহজে হার মানে না (Fighter / Resilient) || অনেক কষ্ট সহ্য করেও দীপা অলিম্পিকে পদক জিতে তার লড়াকু মানসিকতার পরিচয় দিল।</t>
+  </si>
+  <si>
+    <t>শিল্পের গুণযুক্ত (Artistic) || বাঁশ এবং বেতের তৈরি জিনিসগুলোর মধ্যে এক দারুণ শৈল্পিক ছোঁয়া থাকে।</t>
+  </si>
+  <si>
+    <t>যে ভালো চায় (Well-wisher) || বিপদের দিনে একজন প্রকৃত শুভাকাঙ্ক্ষী কখনোই হাত ছেড়ে চলে যায় না।</t>
+  </si>
+  <si>
+    <t>সাধুতা / ন্যায়পরায়ণতা (Honesty) || কাঠুরিয়ার সততা দেখে জলদেবতা তাকে সোনার কুঠার উপহার দিয়েছিলেন।</t>
+  </si>
+  <si>
+    <t>যা হওয়া খুব কঠিন বা অসম্ভব (Remote / Far-fetched) || অলসভাবে বসে থাকলে জীবনে বড় হওয়া বা সফল হওয়া একদম সুদূরপরাহত।</t>
+  </si>
+  <si>
+    <t>দ্বিধাহীন / উদার (Unhesitating / Wholehearted) || অনাথ আশ্রমের শিশুদের জন্য তিনি অকুণ্ঠ সাহায্য দান করলেন।</t>
+  </si>
+  <si>
+    <t>প্রতিজ্ঞা / শপথ (Commitment / Pledge) || পরিবেশ রক্ষায় আমরা সবাই প্লাস্টিক বর্জনের অঙ্গীকার নিলাম।</t>
+  </si>
+  <si>
+    <t>যাকে থামানো যায় না (Unstoppable) || এভারেস্ট বিজয়ীদের মনে পাহাড় চূড়ায় ওঠার এক অদম্য জেদ ছিল।</t>
+  </si>
+  <si>
+    <t>যার কোনো অভিজ্ঞতা নেই (Inexperienced) || নদীটি অত্যন্ত গভীর, তাই কোনো অনভিজ্ঞ চালকের নৌকা চালানো উচিত নয়।</t>
+  </si>
+  <si>
+    <t>নিয়ম বা আদেশ (Commandment / Discipline) || গুরুজনের উপদেশ ও অনুশাসন মেনে চললে জীবনে ভুল কম হয়।</t>
+  </si>
+  <si>
+    <t>আকাশ / শূন্যস্থান (Sky / Space) || হঠাৎ মেঘ কেটে গিয়ে অন্তরীক্ষ জুড়ে এক ঝাঁক তারা ফুটে উঠল।</t>
+  </si>
+  <si>
+    <t>নষ্ট করা (Wastage) || জল আমাদের পরম সম্পদ, তাই এক ফোঁটা জলেরও অপচয় করা অনুচিত।</t>
+  </si>
+  <si>
+    <t>যাকে বাধা দেওয়া যায় না (Irresistible / Unstoppable) || খেলায় ভারতীয় দলের ব্যাটিং আক্রমণ বিপক্ষের কাছে অপ্রতিরোধ্য হয়ে উঠেছিল।</t>
+  </si>
+  <si>
+    <t>কাজ থেকে পাওয়া জ্ঞান (Experience) || দাদুর দীর্ঘ জীবনের অভিজ্ঞতা থেকে আমরা অনেক নতুন গল্প জানতে পারি।</t>
+  </si>
+  <si>
+    <t>স্বাগত জানানো (Reception / Welcome) || স্কুলের বার্ষিক উৎসবে প্রধান অতিথিকে উষ্ণ অভ্যর্থনা জানানো হলো।</t>
+  </si>
+  <si>
+    <t>সম্পূর্ণ / গোড়া থেকে (Radical / Completely) || নতুন প্রযুক্তি আসার ফলে আমাদের জীবনযাত্রার আমূল পরিবর্তন ঘটেছে।</t>
+  </si>
+  <si>
+    <t>ওপরে ওঠা (Climbing / Ascent) || পাহাড়ে আরোহণ করার সময় বিশেষ ধরণের জুতো ও দড়ি ব্যবহার করা হয়।</t>
+  </si>
+  <si>
+    <t>চিন্তার বিষয় / বিপজ্জনক (Critical / Alarming) || ঝড়ের পর নদীর বাঁধের অবস্থা অত্যন্ত আশঙ্কাজনক হয়ে পড়েছে।</t>
+  </si>
+  <si>
+    <t>জড়ানো বা আলিঙ্গন করা (Embraced) || লতানো গাছটি পাশের বড় গাছটিকে শক্ত করে আশ্লিষ্ট করে বড় হচ্ছে।</t>
+  </si>
+  <si>
+    <t>ওপরে ওঠা বা পার হওয়া (Transition / Ascent) || প্রাথমিক বিদ্যালয়ের গণ্ডি পেরিয়ে সে মাধ্যমিক স্তরে উত্তরণ করল।</t>
+  </si>
+  <si>
+    <t>কৌতূহলী / আগ্রহী (Eager / Curious) || জাদুকরের ঝুলি থেকে কী বের হবে, তা দেখতে বাচ্চারা খুব উৎসুক ছিল।</t>
+  </si>
+  <si>
+    <t>আনন্দে আত্মহারা (Overjoyed / Elated) || পরীক্ষায় প্রথম স্থান অধিকার করার খবর শুনে সে উচ্ছ্বসিত হয়ে উঠল।</t>
+  </si>
+  <si>
+    <t>গভীর বা আন্তরিক (Earnest / Sincere) || তোমার ঐকান্তিক চেষ্টা থাকলে এই কঠিন কাজটিও সফল হতে বাধ্য।</t>
+  </si>
+  <si>
+    <t>একসঙ্গে জুটে থাকা (United) || পাড়ার সবাই ঐক্যবদ্ধ হয়ে চোরের হাত থেকে সমাজকে রক্ষা করল।</t>
+  </si>
+  <si>
+    <t>নিষ্ঠুরতা বা কঠিন নিয়ম (Strictness / Harshness) || শরীরচর্চায় নিয়মের কঠোরতা না থাকলে সুস্বাস্থ্য পাওয়া যায় না।</t>
+  </si>
+  <si>
+    <t>বড় সাফল্য বা গৌরব (Achievement / Credit) || ফুটবল টুর্নামেন্টে জেতার সমস্ত কৃতিত্ব দলের কঠোর পরিশ্রমের।</t>
+  </si>
+  <si>
+    <t>যার খুব খিদে পেয়েছে (Hungry) || বন্যায় আটকে পড়া ক্ষুধার্ত মানুষদের কাছে হেলিকপ্টার থেকে খাবার পাঠানো হলো।</t>
+  </si>
+  <si>
+    <t>অসাধারণ গুণের মানুষ যিনি অমর হন (Born under a lucky star / Genius) || স্বামী বিবেকানন্দের মতো ক্ষণজন্মা মহাপুরুষেরা যুগে যুগে পৃথিবীতে আসেন না।</t>
+  </si>
+  <si>
+    <t>আকাশছোঁয়া (Sky-high / Skyscrapers) || মুম্বই শহরে বড় বড় গগনচুম্বী অট্টালিকা দেখতে পাওয়া যায়।</t>
+  </si>
+  <si>
+    <t>মেঘের জমাট ভাব (Gathering of clouds) || বিকেলের আকাশে কালো মেঘের ঘনঘটা দেখে রাখাল দল বাড়ি ফিরল।</t>
+  </si>
+  <si>
+    <t>যা মন হরণ করে (Fascinating / Interesting) || রাজস্থানের প্রাচীন কেল্লাগুলোর ইতিহাস অত্যন্ত চিত্তাকর্ষক।</t>
+  </si>
+  <si>
+    <t>যা ছন্দে বাঁধা (Rhythmic) || কবি সুকুমার রায়ের কবিতাগুলোর ছন্দোবদ্ধ রূপ বাচ্চাদের খুব প্রিয়।</t>
+  </si>
+  <si>
+    <t>মানুষের ভালোবাসা পাওয়া (Popularity) || নিজের মিষ্টি ব্যবহারের কারণে শিক্ষকটি ছাত্রদের মধ্যে খুব জনপ্রিয়তা পেয়েছেন।</t>
+  </si>
+  <si>
+    <t>খুব গুরুত্বপূর্ণ (Significant) || বিজ্ঞানীর এই নতুন আবিষ্কারটি চিকিৎসা শাস্ত্রে অত্যন্ত তাত্পর্যপূর্ণ।</t>
+  </si>
+  <si>
+    <t>যা সহজে ভাঙা বা পার হওয়া যায় না (Impregnable) || প্রাচীনকালে দুর্গের চারপাশে বড় প্রাচীর দিয়ে তা দুর্ভেদ্য করা হতো।</t>
+  </si>
+  <si>
+    <t>ভবিষ্যৎ বোঝার ক্ষমতা (Foresight / Vision) || আমাদের প্রধান শিক্ষকের দূরদৃষ্টির কারণে স্কুলটি আজ জেলায় সেরা।</t>
+  </si>
+  <si>
+    <t>আকাশে ল্যাজবিশিষ্ট জ্যোতিষ্ক (Comet) || অনেক বছর পর পর রাতের আকাশে এক অনন্য ধূমকেতুর দেখা মেলে।</t>
+  </si>
+  <si>
+    <t>যা রোজ কাজে লাগে (Daily essentials) || চাল, ডাল ও তেলের মতো নিত্যপ্রয়োজনীয় জিনিসের দাম বাড়ছে।</t>
+  </si>
+  <si>
+    <t>যে অন্যের ওপর চড়ে বাঁচে (Dependent) || স্বাবলম্বী মানুষ কখনো কারও ওপর পরনির্ভরশীল হয়ে থাকতে চায় না।</t>
+  </si>
+  <si>
+    <t>হারিয়ে দেওয়া (Defeated) || আমাদের দাবাড়ু খুব সহজেই বিপক্ষ দেশের খেলোয়াড়কে পরাস্ত করল।</t>
+  </si>
+  <si>
+    <t>চঞ্চল ও সতেজ (Lively / Energetic) || ছোট্ট শিশুটির প্রাণবন্ত হাসি পুরো ঘরের পরিবেশটাই বদলে দিল।</t>
+  </si>
+  <si>
+    <t>ভালো-মন্দ বিচার করতে পারে যে (Conscious / Conscientious) || একজন বিবেকবান মানুষ কখনোই কারও ক্ষতি করার কথা ভাবেন না।</t>
+  </si>
+  <si>
+    <t>ভরসা করার মতো (Trustworthy / Faithful) || কুকুর মানুষের সবচেয়ে বিশ্বস্ত ও অনুগত প্রাণী হিসেবে পরিচিত।</t>
+  </si>
+  <si>
+    <t>নানান রঙ বা গুণে ভরা (Diverse / Colorful) || ভারতের সংস্কৃতি অত্যন্ত বৈচিত্র্যময়, এখানে নানান ভাষার মানুষ থাকেন।</t>
+  </si>
+  <si>
+    <t>বিজ্ঞানসম্মত (Scientific) || কৃষিকাজে বৈজ্ঞানিক পদ্ধতি ব্যবহার করায় এবার ফসলের ফলন দ্বিগুণ হয়েছে।</t>
+  </si>
+  <si>
+    <t>কাজের মধ্যে থাকা (Busyness) || পরীক্ষার ঠিক আগে ছাত্রছাত্রীদের পড়ার টেবিল ও মনে ব্যস্ততা বেড়ে যায়।</t>
+  </si>
+  <si>
+    <t>মহান নারী (Great / Noble woman) || মাদার টেরেসা ছিলেন এক মহীয়সী নারী, যিনি কুষ্ঠরোগীদের সেবা করতেন।</t>
+  </si>
+  <si>
+    <t>যত্ন নিয়ে বাঁচিয়ে রাখা (Maintenance) || ঐতিহাসিক স্মৃতিস্তম্ভগুলোর সঠিক রক্ষণাবেক্ষণ করা আমাদের কর্তব্য।</t>
+  </si>
+  <si>
+    <t>অপমানের বিষয় (Shameful) || খেলায় নিয়মের বাইরে গিয়ে কাউকে আঘাত করা অত্যন্ত লজ্জাজনক ঘটনা।</t>
+  </si>
+  <si>
+    <t>যা থেকে কিছু শেখা যায় (Educational / Moral lesson) || পঞ্চতন্ত্রের প্রতিটি পশুপাখির গল্পের শেষে একটি শিক্ষণীয় বার্তা থাকে।</t>
+  </si>
+  <si>
+    <t>দেখতে খুব সুন্দর (Beautiful / Ornamental) || আলো দিয়ে সাজানোর পর মণ্ডপটি ভারী শোভাময় দেখাচ্ছিল।</t>
+  </si>
+  <si>
+    <t>শ্রদ্ধা নিবেদন করা (Homage / Tribute) || স্বাধীনতা দিবসের সকালে শহিদ বেদীতে ফুল দিয়ে শ্রদ্ধাঞ্জলি জানানো হলো।</t>
+  </si>
+  <si>
+    <t>যার দুই হাত সমান চলে (Ambidextrous) || মহাভারতের অর্জুন দু-হাতে তির চালাতে পারতেন বলে তাঁকে সব্যসাচী বলা হতো।</t>
+  </si>
+  <si>
+    <t>সর্বোচ্চ ক্ষমতার অধিকারী (Sovereign) || ১৫ই আগস্ট ১৯৪৭ সালে ভারত একটি স্বাধীন ও সার্বভৌম রাষ্ট্র হিসেবে আত্মপ্রকাশ করে।</t>
+  </si>
+  <si>
+    <t>পরিষ্কার ভাব / সততা (Transparency / Clarity) || সরকারি সমস্ত কাজে স্বচ্ছতা বজায় রাখা জরুরি যাতে দুর্নীতি না হয়।</t>
+  </si>
+  <si>
+    <t>অনুপম</t>
+  </si>
+  <si>
+    <t>অকুতোভয়</t>
+  </si>
+  <si>
+    <t>অনাবিল</t>
+  </si>
+  <si>
+    <t>অমলিন</t>
+  </si>
+  <si>
+    <t>অভেদ্য</t>
+  </si>
+  <si>
+    <t>অগ্রগণ্য</t>
+  </si>
+  <si>
+    <t>অমিত</t>
+  </si>
+  <si>
+    <t>অর্পণ</t>
+  </si>
+  <si>
+    <t>অবিচল</t>
+  </si>
+  <si>
+    <t>উৎফুল্ল</t>
+  </si>
+  <si>
+    <t>উন্মেষ</t>
+  </si>
+  <si>
+    <t>ঔজ্জ্বল্য</t>
+  </si>
+  <si>
+    <t>কুশল</t>
+  </si>
+  <si>
+    <t>গরিমা</t>
+  </si>
+  <si>
+    <t>গম্ভীর</t>
+  </si>
+  <si>
+    <t>গৌরব</t>
+  </si>
+  <si>
+    <t>চঞ্চল</t>
+  </si>
+  <si>
+    <t>জ্যোতি</t>
+  </si>
+  <si>
+    <t>তীক্ষ্ণ</t>
+  </si>
+  <si>
+    <t>ত্যাগ</t>
+  </si>
+  <si>
+    <t>দুর্বার</t>
+  </si>
+  <si>
+    <t>নির্মল</t>
+  </si>
+  <si>
+    <t>পরিপাটি</t>
+  </si>
+  <si>
+    <t>প্রখর</t>
+  </si>
+  <si>
+    <t>প্রসন্ন</t>
+  </si>
+  <si>
+    <t>ফলপ্রসূ</t>
+  </si>
+  <si>
+    <t>বিনয়</t>
+  </si>
+  <si>
+    <t>বিমুগ্ধ</t>
+  </si>
+  <si>
+    <t>মহিমা</t>
+  </si>
+  <si>
+    <t>মনন</t>
+  </si>
+  <si>
+    <t>রম্য</t>
+  </si>
+  <si>
+    <t>সজীব</t>
+  </si>
+  <si>
+    <t>স্বনির্ভর</t>
+  </si>
+  <si>
+    <t>অতুলনীয়, যার তুলনা নেই || রবীন্দ্রনাথের সাহিত্য অনুপম।</t>
+  </si>
+  <si>
+    <t>ভয়হীন || সৈনিকটি অকুতোভয় হয়ে যুদ্ধ করল।</t>
+  </si>
+  <si>
+    <t>নির্মল, বিশুদ্ধ || সকালে অনাবিল আনন্দে মাঠে খেললাম।</t>
+  </si>
+  <si>
+    <t>যা মলিন হয় না || মায়ের হাসি আজও অমলিন।</t>
+  </si>
+  <si>
+    <t>ভেদ করা যায় না || দুর্গের প্রাচীর ছিল অভেদ্য।</t>
+  </si>
+  <si>
+    <t>সবার আগে গণ্য || তিনি বিদ্যালয়ের অগ্রগণ্য ছাত্র।</t>
+  </si>
+  <si>
+    <t>দমন করা যায় না || তার অদম্য ইচ্ছাশক্তি সবাইকে অনুপ্রাণিত করে।</t>
+  </si>
+  <si>
+    <t>অপরিসীম || প্রকৃতির অমিত সৌন্দর্য মন ভরিয়ে দেয়।</t>
+  </si>
+  <si>
+    <t>উৎসর্গ করা || আমরা ফুল অর্পণ করলাম।</t>
+  </si>
+  <si>
+    <t>স্থির || বিপদেও সে অবিচল ছিল।</t>
+  </si>
+  <si>
+    <t>দীপ্তিমান || তার উজ্জ্বল ফলাফল সবাইকে খুশি করেছে।</t>
+  </si>
+  <si>
+    <t>শ্রেষ্ঠত্ব || কঠোর পরিশ্রমেই উৎকর্ষ আসে।</t>
+  </si>
+  <si>
+    <t>দয়ালু || উদার মানুষ সবাইকে সাহায্য করেন।</t>
+  </si>
+  <si>
+    <t>আনন্দিত || পুরস্কার পেয়ে সে উৎফুল্ল হয়ে উঠল।</t>
+  </si>
+  <si>
+    <t>সূচনা || বসন্তে নতুন পাতার উন্মেষ ঘটে।</t>
+  </si>
+  <si>
+    <t>মিল, একতা || ঐক্যেই শক্তি।</t>
+  </si>
+  <si>
+    <t>দীপ্তি || সূর্যের ঔজ্জ্বল্য চোখ ধাঁধিয়ে দেয়।</t>
+  </si>
+  <si>
+    <t>উপকার স্মরণকারী || আমি শিক্ষকের প্রতি কৃতজ্ঞ।</t>
+  </si>
+  <si>
+    <t>দক্ষ || তিনি কুশল কারিগর।</t>
+  </si>
+  <si>
+    <t>জানার ইচ্ছা || বিজ্ঞানের প্রতি তার কৌতূহল অনেক।</t>
+  </si>
+  <si>
+    <t>মর্যাদা || দেশের গরিমা রক্ষা করা উচিত।</t>
+  </si>
+  <si>
+    <t>গুরুগম্ভীর || প্রধান শিক্ষক গম্ভীরভাবে কথা বললেন।</t>
+  </si>
+  <si>
+    <t>সম্মান || দেশের জন্য খেলতে পারা গৌরবের।</t>
+  </si>
+  <si>
+    <t>অস্থির || ছোট্ট শিশুটি খুব চঞ্চল।</t>
+  </si>
+  <si>
+    <t>চিরকালীন || সত্য চিরন্তন।</t>
+  </si>
+  <si>
+    <t>আলো || প্রদীপের জ্যোতি ঘর আলোকিত করল।</t>
+  </si>
+  <si>
+    <t>ধারালো || ঈগলের তীক্ষ্ণ দৃষ্টি থাকে।</t>
+  </si>
+  <si>
+    <t>ছেড়ে দেওয়া || মহান মানুষ ত্যাগ করতে জানেন।</t>
+  </si>
+  <si>
+    <t>অপ্রতিরোধ্য || নদীর দুর্বার স্রোত বইছে।</t>
+  </si>
+  <si>
+    <t>সহজে পাওয়া যায় না || এই ফুলটি খুব দুর্লভ।</t>
+  </si>
+  <si>
+    <t>ঘন || নিবিড় অরণ্যে অনেক প্রাণী থাকে।</t>
+  </si>
+  <si>
+    <t>পরিষ্কার || নির্মল আকাশ দেখতে ভালো লাগে।</t>
+  </si>
+  <si>
+    <t>সাহসী || নির্ভীক মানুষ সত্য কথা বলে।</t>
+  </si>
+  <si>
+    <t>দক্ষতা || তার ছবিতে নৈপুণ্য ফুটে উঠেছে।</t>
+  </si>
+  <si>
+    <t>সুন্দরভাবে গুছানো || তার খাতা খুব পরিপাটি।</t>
+  </si>
+  <si>
+    <t>অন্যের উপকার || পরোপকার মহৎ কাজ।</t>
+  </si>
+  <si>
+    <t>তীব্র || আজ রোদের প্রখর তাপ।</t>
+  </si>
+  <si>
+    <t>জ্ঞান ও বুদ্ধি || প্রজ্ঞা মানুষকে সঠিক পথ দেখায়।</t>
+  </si>
+  <si>
+    <t>খুশি || শিক্ষক আমার কাজে প্রসন্ন হলেন।</t>
+  </si>
+  <si>
+    <t>উৎসাহ || বাবার কথা আমাকে প্রেরণা দেয়।</t>
+  </si>
+  <si>
+    <t>সফল || আমাদের আলোচনা ফলপ্রসূ হয়েছে।</t>
+  </si>
+  <si>
+    <t>নম্রতা || বিনয় মানুষের বড় গুণ।</t>
+  </si>
+  <si>
+    <t>মুগ্ধ || সুন্দর দৃশ্য দেখে সবাই বিমুগ্ধ।</t>
+  </si>
+  <si>
+    <t>গৌরব || প্রকৃতির মহিমা অপরিসীম।</t>
+  </si>
+  <si>
+    <t>চিন্তাশক্তি || বই পড়লে মনন বৃদ্ধি পায়।</t>
+  </si>
+  <si>
+    <t>কম খরচ করেন যিনি || মিতব্যয়ী হওয়া ভালো অভ্যাস।</t>
+  </si>
+  <si>
+    <t>মনোরম || গ্রামের রম্য পরিবেশ সবাইকে টানে।</t>
+  </si>
+  <si>
+    <t>প্রাণবন্ত || বৃষ্টির পরে প্রকৃতি সজীব হয়ে ওঠে।</t>
+  </si>
+  <si>
+    <t>বন্ধুত্বপূর্ণ সম্পর্ক || আমাদের মধ্যে সৌহার্দ্য বজায় রাখা উচিত।</t>
+  </si>
+  <si>
+    <t>নিজের ওপর নির্ভরশীল || আমাদের স্বনির্ভর হওয়া উচিত।</t>
+  </si>
+  <si>
+    <t>অর্থ লেখো ও বাক্য রচনা করো।</t>
+  </si>
+  <si>
+    <t>১. একই বানান অথচ ভিন্ন অর্থ এবং বাক্যে প্রয়োগ।</t>
+  </si>
+  <si>
+    <t>২. চিঠি লেখঃ ক) প্রধান শিক্ষককে, খ) বন্ধুকে, গ) বাবা-মাকে</t>
+  </si>
+  <si>
+    <t>৩. কোনো কবিতার অংশকে বা গদ্যের অংশকে পড়ে নিজের ভাষায় লেখা</t>
+  </si>
+  <si>
+    <t>৪. বাক্যে নানারকম ভুল সংশোধন</t>
+  </si>
+  <si>
+    <t>৫. বাক্যে পদ বিন্যাস</t>
+  </si>
+  <si>
+    <t>৮. বিপরীতার্থক শব্দ</t>
+  </si>
+  <si>
+    <t>৯. বানান</t>
+  </si>
+  <si>
+    <t>১০. বোধ পরীক্ষণ</t>
+  </si>
+  <si>
+    <t>১১. হাতের লেখা</t>
+  </si>
+  <si>
+    <t>১২. বর্ণপরিচয়, (যুক্তব্যঞ্জন সহ)</t>
+  </si>
+  <si>
+    <t>১৩. বর্ণ বিশ্লেষণ</t>
+  </si>
+  <si>
+    <t>১৪. পদ পরিচয়</t>
+  </si>
+  <si>
+    <t>১৫. এককথায় লেখা</t>
+  </si>
+  <si>
+    <t>১৬. পদান্তর</t>
+  </si>
+  <si>
+    <t>১৭. সমোচ্চারিত ভিন্ন অর্থবোধক শব্দ</t>
+  </si>
+  <si>
+    <t>১৮. প্রতিশব্দ বা সমার্থক শব্দ</t>
+  </si>
+  <si>
+    <t>১৯. সূত্রসহ স্বরসন্ধি</t>
+  </si>
+  <si>
+    <t>২০. লিঙ্গ, বচন, পুরুষ</t>
+  </si>
+  <si>
+    <t>২৩. শব্দের বিশিষ্টাৰ্থে প্ৰয়োগ</t>
+  </si>
+  <si>
+    <t>২৪. স্বচ্ছন্দ রচনা</t>
+  </si>
+  <si>
+    <t>২২. যতিচিহ্ন</t>
+  </si>
+  <si>
+    <t xml:space="preserve">২১. সাধু ও চলিতভাষা </t>
+  </si>
+  <si>
+    <t>Syllabus</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">৬. প্রদত্ত শব্দের সাহায্যে বাক্যরচনা </t>
+  </si>
+  <si>
+    <t>৭. শব্দার্থ</t>
+  </si>
+  <si>
+    <t>এক কথায় প্রকাশ</t>
+  </si>
+  <si>
+    <t>সন্ধি বিচ্ছেদ করো।</t>
+  </si>
+  <si>
+    <t>অকর্মক</t>
+  </si>
+  <si>
+    <t>সকর্মক</t>
+  </si>
+  <si>
+    <t>অক্ষম</t>
+  </si>
+  <si>
+    <t>পশ্চাৎ</t>
+  </si>
+  <si>
+    <t>অচল</t>
+  </si>
+  <si>
+    <t>সচল</t>
+  </si>
+  <si>
+    <t>অচলায়তন</t>
+  </si>
+  <si>
+    <t>সচলায়তন</t>
+  </si>
+  <si>
+    <t>অচেতন</t>
+  </si>
+  <si>
+    <t>সচেতন</t>
+  </si>
+  <si>
+    <t>অজ্ঞ</t>
+  </si>
+  <si>
+    <t>প্রাজ্ঞ</t>
+  </si>
+  <si>
+    <t>বৃহৎ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">অতিকায় </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ক্ষুদ্রকায় </t>
+  </si>
+  <si>
+    <t>অতিবৃষ্টি</t>
+  </si>
+  <si>
+    <t>অনাবৃষ্টি</t>
+  </si>
+  <si>
+    <t>অতীত</t>
+  </si>
+  <si>
+    <t>ভবিষ্যত</t>
+  </si>
+  <si>
+    <t>অদ্য</t>
+  </si>
+  <si>
+    <t>কল্য</t>
+  </si>
+  <si>
+    <t>অধঃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ঊর্ধ্ব </t>
+  </si>
+  <si>
+    <t>অধম</t>
+  </si>
+  <si>
+    <t>উত্তম</t>
+  </si>
+  <si>
+    <t xml:space="preserve">উত্তমর্ণ </t>
+  </si>
+  <si>
+    <t>অধিত্যকা</t>
+  </si>
+  <si>
+    <t>অনন্ত</t>
+  </si>
+  <si>
+    <t>সান্ত</t>
+  </si>
+  <si>
+    <t>প্রতিকূল</t>
+  </si>
+  <si>
+    <t>অনুগ্রহ</t>
+  </si>
+  <si>
+    <t>নিগ্রহ</t>
+  </si>
+  <si>
+    <t>বিরক্ত</t>
+  </si>
+  <si>
+    <t>বিরাগ</t>
+  </si>
+  <si>
+    <t>অনুলোম</t>
+  </si>
+  <si>
+    <t>প্রতিলোম</t>
+  </si>
+  <si>
+    <t>অলীক</t>
+  </si>
+  <si>
+    <t>সত্য</t>
+  </si>
+  <si>
+    <t>অল্পপ্রাণ</t>
+  </si>
+  <si>
+    <t>মহাপ্রাণ</t>
+  </si>
+  <si>
+    <t>অশন</t>
+  </si>
+  <si>
+    <t>অনশন</t>
+  </si>
+  <si>
+    <t>সসীম</t>
+  </si>
+  <si>
+    <t>অস্তগামী</t>
+  </si>
+  <si>
+    <t>উদীয়মান</t>
+  </si>
+  <si>
+    <t>অস্তি</t>
+  </si>
+  <si>
+    <t>নাস্তি/নেতি</t>
+  </si>
+  <si>
+    <t>অহিংস</t>
+  </si>
+  <si>
+    <t>সহিংস</t>
+  </si>
+  <si>
+    <t>আকর্ষণ</t>
+  </si>
+  <si>
+    <t>বিকর্ষণ</t>
+  </si>
+  <si>
+    <t>আকুঞ্চন</t>
+  </si>
+  <si>
+    <t>প্রসারণ</t>
+  </si>
+  <si>
+    <t>আগত</t>
+  </si>
+  <si>
+    <t>অনাগত</t>
+  </si>
+  <si>
+    <t>আগমন</t>
+  </si>
+  <si>
+    <t>প্রস্থান</t>
+  </si>
+  <si>
+    <t>আজ</t>
+  </si>
+  <si>
+    <t>কাল</t>
+  </si>
+  <si>
+    <t>আত্ম</t>
+  </si>
+  <si>
+    <t>পর</t>
+  </si>
+  <si>
+    <t>আত্মীয়</t>
+  </si>
+  <si>
+    <t>অনাত্মীয়</t>
+  </si>
+  <si>
+    <t>আদি</t>
+  </si>
+  <si>
+    <t>অন্ত</t>
+  </si>
+  <si>
+    <t>বিপরীতার্থক শব্দ লেখো।</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -23048,6 +24685,29 @@
       <name val="Nirmala UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -23063,7 +24723,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -23071,11 +24731,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -23096,8 +24772,32 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -23376,6 +25076,4404 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="68.85546875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="11" style="13" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>4871</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>4849</v>
+      </c>
+      <c r="B2" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>4850</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>4851</v>
+      </c>
+      <c r="B4" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>4852</v>
+      </c>
+      <c r="B5" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>4853</v>
+      </c>
+      <c r="B6" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>4873</v>
+      </c>
+      <c r="B7" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>4874</v>
+      </c>
+      <c r="B8" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>4854</v>
+      </c>
+      <c r="B9" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>4855</v>
+      </c>
+      <c r="B10" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>4856</v>
+      </c>
+      <c r="B11" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>4857</v>
+      </c>
+      <c r="B12" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>4858</v>
+      </c>
+      <c r="B13" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>4859</v>
+      </c>
+      <c r="B14" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>4860</v>
+      </c>
+      <c r="B15" s="13">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>4861</v>
+      </c>
+      <c r="B16" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>4862</v>
+      </c>
+      <c r="B17" s="13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>4863</v>
+      </c>
+      <c r="B18" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>4864</v>
+      </c>
+      <c r="B19" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>4865</v>
+      </c>
+      <c r="B20" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>4866</v>
+      </c>
+      <c r="B21" s="13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>4870</v>
+      </c>
+      <c r="B22" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>4869</v>
+      </c>
+      <c r="B23" s="13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>4867</v>
+      </c>
+      <c r="B24" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>4868</v>
+      </c>
+      <c r="B25" s="13">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A7" location="'অর্থ ও বাক্য রচনা'!A1" display="৬. প্রদত্ত শব্দের সাহায্যে বাক্যরচনা "/>
+    <hyperlink ref="A17" location="পদান্তর!A1" display="১৬. পদান্তর"/>
+    <hyperlink ref="A19" location="'সমার্থক শব্দ'!A1" display="১৮. প্রতিশব্দ বা সমার্থক শব্দ"/>
+    <hyperlink ref="A16" location="'এক কথায় প্রকাশ (Guide)'!A1" display="১৫. এককথায় লেখা"/>
+    <hyperlink ref="A20" location="স্বরসন্ধি!A1" display="১৯. সূত্রসহ স্বরসন্ধি"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B144"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>2693</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>2697</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>2709</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>2711</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>2713</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>2718</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>2721</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>2723</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>2725</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>2727</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>2729</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>2731</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>2732</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>2733</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>2736</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>2738</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>2739</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>2740</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>2742</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>2747</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>2749</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>2751</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>2753</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>2755</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>2757</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>2759</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>2761</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>2763</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>2765</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>2767</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>2769</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>2771</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>2773</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>2775</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>2779</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>2781</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>2783</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>2785</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>2786</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>2792</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>2796</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>2798</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>2802</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>2814</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>2815</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>2816</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>2819</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>2821</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>2823</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>2824</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>2825</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>2827</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>2829</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>2831</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>2833</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>2837</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>2838</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>2839</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>2841</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>2842</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>2843</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>2847</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>2851</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>2853</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>2857</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>2859</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>2861</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>2863</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>2865</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>2867</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>2868</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>2869</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>2871</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>2873</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>2876</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>2878</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>2880</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>2882</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>2884</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>2885</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>2886</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>2889</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>2890</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>2891</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>2892</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>2901</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>2902</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>2904</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>2905</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>2747</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>2907</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>2908</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>2909</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>2912</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>2914</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>2916</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>2918</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>2919</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>2920</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>2921</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>2924</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>2926</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>2928</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>2936</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>2938</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>2939</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>2942</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>2944</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>2945</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>2946</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>2947</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>2948</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>2949</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>2952</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>2953</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>2954</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>2955</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>2956</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>2957</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>2958</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>2959</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>2961</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>2963</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>2964</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>2965</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>2967</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>2970</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B144"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B80"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B78" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B79" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B80"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B251"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="143.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>4848</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>4564</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>4524</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>4715</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>4766</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>4799</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>4443</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>4615</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>4770</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>4803</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>4444</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>4616</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>4525</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>4716</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>994</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>4666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>994</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>4717</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>994</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>4804</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>4445</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>4617</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>4526</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>4718</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>4767</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>4485</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>4667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>4398</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>4565</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>4765</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>4798</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>3122</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>4618</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>4527</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>4719</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>4446</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>4619</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>4528</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>4720</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>4486</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>4668</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>4529</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>4721</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>4447</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>4620</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>4621</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>4530</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>4722</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>4484</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>4665</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>4773</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>4807</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>4400</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>4567</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>4531</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>4723</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>4487</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>4669</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>4448</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>4622</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>4449</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>4623</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>4769</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>4802</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>4532</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>4724</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>4768</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>4801</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>4771</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>4805</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>4772</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>4806</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>4450</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>4624</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
+        <v>3074</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>4568</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>4401</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>4569</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>4402</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>4570</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>4488</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>4670</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
+        <v>4489</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>4671</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>4533</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>4725</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
+        <v>3242</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>4726</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>4451</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>4625</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>4534</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>4727</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>4490</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>4672</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>3256</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>4626</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>4535</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>4728</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>4491</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>4673</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>2831</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>4731</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>4808</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>4452</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>4627</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
+        <v>3309</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
+        <v>3311</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>4675</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>3311</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>4809</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>4774</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
+        <v>4453</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>4628</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>4537</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>4730</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>4536</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>4729</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>3360</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>4810</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>4492</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>4676</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="11" t="s">
+        <v>4403</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>4571</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>4404</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>4572</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
+        <v>4405</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>4573</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>4775</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>4812</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>4493</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>4677</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>4538</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>4732</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>3923</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>4813</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>4539</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>4733</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>4629</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
+        <v>4494</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>4678</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
+        <v>4454</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>4630</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>4776</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>4814</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>4540</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>4734</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
+        <v>4455</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>4631</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="11" t="s">
+        <v>4456</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>4632</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="11" t="s">
+        <v>4457</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>4633</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>4777</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>4816</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>4815</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="11" t="s">
+        <v>4407</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>4575</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="11" t="s">
+        <v>4541</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>4735</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="11" t="s">
+        <v>4406</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>4574</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
+        <v>4406</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>4817</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="11" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>4737</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="11" t="s">
+        <v>4495</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>4679</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="11" t="s">
+        <v>4408</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>4576</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="11" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>4736</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="11" t="s">
+        <v>4496</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>4680</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="11" t="s">
+        <v>4542</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="11" t="s">
+        <v>4458</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>4634</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="11" t="s">
+        <v>4459</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>4635</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="12" t="s">
+        <v>4779</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>4819</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>4778</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>4818</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="11" t="s">
+        <v>4409</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>4577</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>4780</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>4820</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="11" t="s">
+        <v>4460</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>4636</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="11" t="s">
+        <v>4543</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>4739</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="12" t="s">
+        <v>4781</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>4821</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="11" t="s">
+        <v>4410</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>4578</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="11" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="11" t="s">
+        <v>4331</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>4681</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="11" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>4741</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="11" t="s">
+        <v>4497</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>4682</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="11" t="s">
+        <v>4544</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>4742</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="11" t="s">
+        <v>880</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="11" t="s">
+        <v>3467</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>4683</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="11" t="s">
+        <v>4461</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>4638</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="11" t="s">
+        <v>923</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>4639</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>4579</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="11" t="s">
+        <v>4498</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>4684</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="12" t="s">
+        <v>4782</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>4823</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="11" t="s">
+        <v>4411</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>4580</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="11" t="s">
+        <v>4462</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>4640</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="11" t="s">
+        <v>950</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>4685</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="11" t="s">
+        <v>4545</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>4743</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="11" t="s">
+        <v>4412</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>4581</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="11" t="s">
+        <v>4499</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>4686</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="12" t="s">
+        <v>4783</v>
+      </c>
+      <c r="B122" s="12" t="s">
+        <v>4824</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="11" t="s">
+        <v>4413</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>4582</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="11" t="s">
+        <v>4463</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>4641</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="12" t="s">
+        <v>4784</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>4825</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="11" t="s">
+        <v>2727</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>4642</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="11" t="s">
+        <v>4415</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>4584</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="11" t="s">
+        <v>4500</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="11" t="s">
+        <v>4414</v>
+      </c>
+      <c r="B129" s="11" t="s">
+        <v>4583</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="12" t="s">
+        <v>4785</v>
+      </c>
+      <c r="B130" s="12" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="11" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B131" s="11" t="s">
+        <v>4744</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="11" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>4643</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="12" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B133" s="12" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="11" t="s">
+        <v>4464</v>
+      </c>
+      <c r="B134" s="11" t="s">
+        <v>4644</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="11" t="s">
+        <v>4416</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>4585</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="11" t="s">
+        <v>4546</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>4745</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="11" t="s">
+        <v>4501</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>4688</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="11" t="s">
+        <v>4503</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>4690</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="11" t="s">
+        <v>4502</v>
+      </c>
+      <c r="B139" s="11" t="s">
+        <v>4689</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="11" t="s">
+        <v>4465</v>
+      </c>
+      <c r="B140" s="11" t="s">
+        <v>4645</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="11" t="s">
+        <v>4466</v>
+      </c>
+      <c r="B141" s="11" t="s">
+        <v>4646</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="11" t="s">
+        <v>4504</v>
+      </c>
+      <c r="B142" s="11" t="s">
+        <v>4691</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="11" t="s">
+        <v>4547</v>
+      </c>
+      <c r="B143" s="11" t="s">
+        <v>4746</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="11" t="s">
+        <v>3537</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>4586</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="11" t="s">
+        <v>4505</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>4692</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="11" t="s">
+        <v>4417</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>4587</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="11" t="s">
+        <v>4506</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>4693</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="11" t="s">
+        <v>4548</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>4747</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="11" t="s">
+        <v>4419</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>4589</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="12" t="s">
+        <v>3991</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>4828</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="11" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B151" s="11" t="s">
+        <v>4694</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="11" t="s">
+        <v>4418</v>
+      </c>
+      <c r="B152" s="11" t="s">
+        <v>4588</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="12" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>4830</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="12" t="s">
+        <v>4786</v>
+      </c>
+      <c r="B154" s="12" t="s">
+        <v>4829</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="11" t="s">
+        <v>4508</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>4695</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="11" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>4647</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="12" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>4831</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="11" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>4648</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="11" t="s">
+        <v>4549</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="11" t="s">
+        <v>4550</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>4749</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="11" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="12" t="s">
+        <v>4787</v>
+      </c>
+      <c r="B162" s="12" t="s">
+        <v>4832</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="11" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>4651</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="11" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>4649</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="11" t="s">
+        <v>4420</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="11" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B166" s="11" t="s">
+        <v>4696</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="12" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B167" s="12" t="s">
+        <v>4833</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="11" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B168" s="11" t="s">
+        <v>4697</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="11" t="s">
+        <v>4510</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>4698</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="12" t="s">
+        <v>4788</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>4834</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>4835</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="11" t="s">
+        <v>4474</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>4654</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="11" t="s">
+        <v>4473</v>
+      </c>
+      <c r="B173" s="11" t="s">
+        <v>4653</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="11" t="s">
+        <v>4422</v>
+      </c>
+      <c r="B174" s="11" t="s">
+        <v>4592</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="11" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B175" s="11" t="s">
+        <v>4652</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="11" t="s">
+        <v>4511</v>
+      </c>
+      <c r="B176" s="11" t="s">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="11" t="s">
+        <v>4421</v>
+      </c>
+      <c r="B177" s="11" t="s">
+        <v>4591</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="11" t="s">
+        <v>3588</v>
+      </c>
+      <c r="B178" s="11" t="s">
+        <v>4593</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="11" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B179" s="11" t="s">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B180" s="11" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="11" t="s">
+        <v>4423</v>
+      </c>
+      <c r="B181" s="11" t="s">
+        <v>4594</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="11" t="s">
+        <v>4424</v>
+      </c>
+      <c r="B182" s="11" t="s">
+        <v>4595</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="12" t="s">
+        <v>4789</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>4836</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="11" t="s">
+        <v>4551</v>
+      </c>
+      <c r="B184" s="11" t="s">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="11" t="s">
+        <v>4475</v>
+      </c>
+      <c r="B185" s="11" t="s">
+        <v>4655</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="12" t="s">
+        <v>4475</v>
+      </c>
+      <c r="B186" s="12" t="s">
+        <v>4837</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="11" t="s">
+        <v>4512</v>
+      </c>
+      <c r="B187" s="11" t="s">
+        <v>4702</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="12" t="s">
+        <v>4790</v>
+      </c>
+      <c r="B188" s="12" t="s">
+        <v>4838</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="11" t="s">
+        <v>4476</v>
+      </c>
+      <c r="B189" s="11" t="s">
+        <v>4656</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="11" t="s">
+        <v>4513</v>
+      </c>
+      <c r="B190" s="11" t="s">
+        <v>4703</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="11" t="s">
+        <v>4514</v>
+      </c>
+      <c r="B191" s="11" t="s">
+        <v>4704</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="11" t="s">
+        <v>4477</v>
+      </c>
+      <c r="B192" s="11" t="s">
+        <v>4657</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="11" t="s">
+        <v>4515</v>
+      </c>
+      <c r="B193" s="11" t="s">
+        <v>4705</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="11" t="s">
+        <v>4425</v>
+      </c>
+      <c r="B194" s="11" t="s">
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="11" t="s">
+        <v>4516</v>
+      </c>
+      <c r="B195" s="11" t="s">
+        <v>4706</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="11" t="s">
+        <v>4428</v>
+      </c>
+      <c r="B196" s="11" t="s">
+        <v>4599</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="12" t="s">
+        <v>4791</v>
+      </c>
+      <c r="B197" s="12" t="s">
+        <v>4839</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="11" t="s">
+        <v>4552</v>
+      </c>
+      <c r="B198" s="11" t="s">
+        <v>4751</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="12" t="s">
+        <v>4792</v>
+      </c>
+      <c r="B199" s="12" t="s">
+        <v>4840</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="11" t="s">
+        <v>4427</v>
+      </c>
+      <c r="B200" s="11" t="s">
+        <v>4598</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="11" t="s">
+        <v>3674</v>
+      </c>
+      <c r="B201" s="11" t="s">
+        <v>4752</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="11" t="s">
+        <v>4517</v>
+      </c>
+      <c r="B202" s="11" t="s">
+        <v>4707</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="11" t="s">
+        <v>4426</v>
+      </c>
+      <c r="B203" s="11" t="s">
+        <v>4597</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="11" t="s">
+        <v>4478</v>
+      </c>
+      <c r="B204" s="11" t="s">
+        <v>4658</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="11" t="s">
+        <v>4553</v>
+      </c>
+      <c r="B205" s="11" t="s">
+        <v>4753</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="11" t="s">
+        <v>4554</v>
+      </c>
+      <c r="B206" s="11" t="s">
+        <v>4754</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="11" t="s">
+        <v>4479</v>
+      </c>
+      <c r="B207" s="11" t="s">
+        <v>4659</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="11" t="s">
+        <v>4555</v>
+      </c>
+      <c r="B208" s="11" t="s">
+        <v>4755</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="12" t="s">
+        <v>4794</v>
+      </c>
+      <c r="B209" s="12" t="s">
+        <v>4842</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="11" t="s">
+        <v>4518</v>
+      </c>
+      <c r="B210" s="11" t="s">
+        <v>4708</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="11" t="s">
+        <v>4429</v>
+      </c>
+      <c r="B211" s="11" t="s">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="11" t="s">
+        <v>4430</v>
+      </c>
+      <c r="B212" s="11" t="s">
+        <v>4601</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="11" t="s">
+        <v>4431</v>
+      </c>
+      <c r="B213" s="11" t="s">
+        <v>4602</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="12" t="s">
+        <v>4793</v>
+      </c>
+      <c r="B214" s="12" t="s">
+        <v>4841</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="11" t="s">
+        <v>4556</v>
+      </c>
+      <c r="B215" s="11" t="s">
+        <v>4756</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="12" t="s">
+        <v>4095</v>
+      </c>
+      <c r="B216" s="12" t="s">
+        <v>4843</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="11" t="s">
+        <v>4432</v>
+      </c>
+      <c r="B217" s="11" t="s">
+        <v>4603</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="11" t="s">
+        <v>4433</v>
+      </c>
+      <c r="B218" s="11" t="s">
+        <v>4604</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="11" t="s">
+        <v>4519</v>
+      </c>
+      <c r="B219" s="11" t="s">
+        <v>4709</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="11" t="s">
+        <v>4557</v>
+      </c>
+      <c r="B220" s="11" t="s">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="12" t="s">
+        <v>4795</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>4844</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="11" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B222" s="11" t="s">
+        <v>4605</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="11" t="s">
+        <v>4558</v>
+      </c>
+      <c r="B223" s="11" t="s">
+        <v>4758</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="11" t="s">
+        <v>4520</v>
+      </c>
+      <c r="B224" s="11" t="s">
+        <v>4710</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="11" t="s">
+        <v>4559</v>
+      </c>
+      <c r="B225" s="11" t="s">
+        <v>4759</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="11" t="s">
+        <v>4435</v>
+      </c>
+      <c r="B226" s="11" t="s">
+        <v>4606</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="11" t="s">
+        <v>4343</v>
+      </c>
+      <c r="B227" s="11" t="s">
+        <v>4712</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="11" t="s">
+        <v>4480</v>
+      </c>
+      <c r="B228" s="11" t="s">
+        <v>4660</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="11" t="s">
+        <v>4521</v>
+      </c>
+      <c r="B229" s="11" t="s">
+        <v>4711</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="11" t="s">
+        <v>3792</v>
+      </c>
+      <c r="B230" s="11" t="s">
+        <v>4607</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="11" t="s">
+        <v>4560</v>
+      </c>
+      <c r="B231" s="11" t="s">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="11" t="s">
+        <v>4561</v>
+      </c>
+      <c r="B232" s="11" t="s">
+        <v>4761</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="11" t="s">
+        <v>4436</v>
+      </c>
+      <c r="B233" s="11" t="s">
+        <v>4608</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="11" t="s">
+        <v>4481</v>
+      </c>
+      <c r="B234" s="11" t="s">
+        <v>4662</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="11" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B235" s="11" t="s">
+        <v>4661</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="12" t="s">
+        <v>4796</v>
+      </c>
+      <c r="B236" s="12" t="s">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="11" t="s">
+        <v>4522</v>
+      </c>
+      <c r="B237" s="11" t="s">
+        <v>4713</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="11" t="s">
+        <v>4437</v>
+      </c>
+      <c r="B238" s="11" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="B239" s="11" t="s">
+        <v>4762</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="11" t="s">
+        <v>4438</v>
+      </c>
+      <c r="B240" s="11" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="11" t="s">
+        <v>4439</v>
+      </c>
+      <c r="B241" s="11" t="s">
+        <v>4611</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="11" t="s">
+        <v>4562</v>
+      </c>
+      <c r="B242" s="11" t="s">
+        <v>4763</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="11" t="s">
+        <v>4523</v>
+      </c>
+      <c r="B243" s="11" t="s">
+        <v>4714</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="11" t="s">
+        <v>4482</v>
+      </c>
+      <c r="B244" s="11" t="s">
+        <v>4663</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="11" t="s">
+        <v>4440</v>
+      </c>
+      <c r="B245" s="11" t="s">
+        <v>4612</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="11" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B246" s="11" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="12" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B247" s="12" t="s">
+        <v>4846</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="11" t="s">
+        <v>4563</v>
+      </c>
+      <c r="B248" s="11" t="s">
+        <v>4764</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="11" t="s">
+        <v>4483</v>
+      </c>
+      <c r="B249" s="11" t="s">
+        <v>4664</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="12" t="s">
+        <v>4797</v>
+      </c>
+      <c r="B250" s="12" t="s">
+        <v>4847</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="11" t="s">
+        <v>4442</v>
+      </c>
+      <c r="B251" s="11" t="s">
+        <v>4614</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C201"/>
+  <sortState ref="A2:B251">
+    <sortCondition ref="A2:A251"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4942</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4877</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4878</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4879</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3100</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4881</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4882</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4883</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4884</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4885</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4886</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4887</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4888</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3097</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4889</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4890</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4891</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4892</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4893</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4894</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4895</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4896</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4897</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4898</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4899</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4900</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4901</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4902</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4903</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4904</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4905</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3884</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4906</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4907</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4908</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>3145</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4909</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>3144</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4911</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4912</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4913</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4914</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4915</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4916</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4917</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4918</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4919</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4920</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4921</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4922</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4923</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>4924</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>4926</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4927</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>4928</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4929</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>4930</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4931</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>4932</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4933</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>4934</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4935</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>4936</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4937</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>4938</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4939</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>4940</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4941</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -23806,7 +29904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B565"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28342,20 +34440,30 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C184"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
+        <v>4875</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>4193</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>4194</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
@@ -28864,7 +34972,7 @@
     </row>
     <row r="65" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>4195</v>
+        <v>4194</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>1139</v>
@@ -28872,7 +34980,7 @@
     </row>
     <row r="66" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>4196</v>
+        <v>4195</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>1595</v>
@@ -28880,23 +34988,23 @@
     </row>
     <row r="67" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
+        <v>4196</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>4197</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>4198</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
+        <v>4198</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>4199</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>4200</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>4201</v>
+        <v>4200</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>1222</v>
@@ -28904,15 +35012,15 @@
     </row>
     <row r="70" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
+        <v>4201</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>4202</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>4203</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>4204</v>
+        <v>4203</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>1006</v>
@@ -28920,7 +35028,7 @@
     </row>
     <row r="72" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>4205</v>
+        <v>4204</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>1817</v>
@@ -28928,23 +35036,23 @@
     </row>
     <row r="73" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
+        <v>4205</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>4206</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>4207</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
+        <v>4207</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>4208</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>4209</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>4210</v>
+        <v>4209</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>159</v>
@@ -28952,15 +35060,15 @@
     </row>
     <row r="76" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
+        <v>4210</v>
+      </c>
+      <c r="B76" s="6" t="s">
         <v>4211</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>4212</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>4213</v>
+        <v>4212</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>149</v>
@@ -28968,31 +35076,31 @@
     </row>
     <row r="78" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
+        <v>4213</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>4214</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>4215</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
+        <v>4215</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>4216</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>4217</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
+        <v>4217</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>4218</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>4219</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>4220</v>
+        <v>4219</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>194</v>
@@ -29000,39 +35108,39 @@
     </row>
     <row r="82" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
+        <v>4220</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>4221</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>4222</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
+        <v>4222</v>
+      </c>
+      <c r="B83" s="6" t="s">
         <v>4223</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>4224</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
+        <v>4224</v>
+      </c>
+      <c r="B84" s="6" t="s">
         <v>4225</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>4226</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
+        <v>4226</v>
+      </c>
+      <c r="B85" s="6" t="s">
         <v>4227</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>4228</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>184</v>
@@ -29040,7 +35148,7 @@
     </row>
     <row r="87" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>3923</v>
@@ -29048,39 +35156,39 @@
     </row>
     <row r="88" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
+        <v>4230</v>
+      </c>
+      <c r="B88" s="6" t="s">
         <v>4231</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>4232</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
+        <v>4232</v>
+      </c>
+      <c r="B89" s="6" t="s">
         <v>4233</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>4234</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
+        <v>4234</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>4235</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>4236</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
+        <v>4236</v>
+      </c>
+      <c r="B91" s="6" t="s">
         <v>4237</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>4238</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>90</v>
@@ -29088,96 +35196,96 @@
     </row>
     <row r="93" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>4253</v>
+        <v>4252</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
+        <v>4240</v>
+      </c>
+      <c r="B94" s="6" t="s">
         <v>4241</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>4242</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
+        <v>4242</v>
+      </c>
+      <c r="B95" s="6" t="s">
         <v>4243</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>4244</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
+        <v>4244</v>
+      </c>
+      <c r="B96" s="6" t="s">
         <v>4245</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>4246</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
+        <v>4246</v>
+      </c>
+      <c r="B97" s="6" t="s">
         <v>4247</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>4248</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
+        <v>4248</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>4249</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>4250</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
+        <v>4250</v>
+      </c>
+      <c r="B99" s="6" t="s">
         <v>4251</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>4252</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
+        <v>4253</v>
+      </c>
+      <c r="B100" s="6" t="s">
         <v>4254</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>4255</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
+        <v>4255</v>
+      </c>
+      <c r="B101" t="s">
         <v>4256</v>
-      </c>
-      <c r="B101" t="s">
-        <v>4257</v>
       </c>
       <c r="C101" s="6"/>
     </row>
     <row r="102" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
+        <v>4257</v>
+      </c>
+      <c r="B102" s="6" t="s">
         <v>4258</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>4259</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
+        <v>4259</v>
+      </c>
+      <c r="B103" s="6" t="s">
         <v>4260</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>4261</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>4262</v>
+        <v>4261</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>870</v>
@@ -29185,48 +35293,48 @@
     </row>
     <row r="105" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
+        <v>4262</v>
+      </c>
+      <c r="B105" t="s">
         <v>4263</v>
-      </c>
-      <c r="B105" t="s">
-        <v>4264</v>
       </c>
       <c r="C105" s="6"/>
     </row>
     <row r="106" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
+        <v>4264</v>
+      </c>
+      <c r="B106" s="6" t="s">
         <v>4265</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>4266</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
+        <v>4266</v>
+      </c>
+      <c r="B107" s="6" t="s">
         <v>4267</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>4268</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
+        <v>4268</v>
+      </c>
+      <c r="B108" s="6" t="s">
         <v>4269</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>4270</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
+        <v>4270</v>
+      </c>
+      <c r="B109" s="6" t="s">
         <v>4271</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>4272</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>4273</v>
+        <v>4272</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>266</v>
@@ -29234,39 +35342,39 @@
     </row>
     <row r="111" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
+        <v>4273</v>
+      </c>
+      <c r="B111" s="6" t="s">
         <v>4274</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>4275</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
+        <v>4275</v>
+      </c>
+      <c r="B112" s="6" t="s">
         <v>4276</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>4277</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
+        <v>4277</v>
+      </c>
+      <c r="B113" s="6" t="s">
         <v>4278</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>4279</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
+        <v>4279</v>
+      </c>
+      <c r="B114" s="6" t="s">
         <v>4280</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>4281</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
-        <v>4282</v>
+        <v>4281</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>82</v>
@@ -29274,31 +35382,31 @@
     </row>
     <row r="116" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
+        <v>4282</v>
+      </c>
+      <c r="B116" s="6" t="s">
         <v>4283</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>4284</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>4397</v>
+        <v>4396</v>
       </c>
       <c r="B117" t="s">
-        <v>4396</v>
+        <v>4395</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
+        <v>4284</v>
+      </c>
+      <c r="B118" s="6" t="s">
         <v>4285</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>4286</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>4287</v>
+        <v>4286</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>704</v>
@@ -29306,16 +35414,16 @@
     </row>
     <row r="120" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
+        <v>4287</v>
+      </c>
+      <c r="B120" t="s">
         <v>4288</v>
-      </c>
-      <c r="B120" t="s">
-        <v>4289</v>
       </c>
       <c r="C120" s="6"/>
     </row>
     <row r="121" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
-        <v>4290</v>
+        <v>4289</v>
       </c>
       <c r="B121" t="s">
         <v>87</v>
@@ -29324,66 +35432,66 @@
     </row>
     <row r="122" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
+        <v>4290</v>
+      </c>
+      <c r="B122" s="6" t="s">
         <v>4291</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>4292</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
+        <v>4292</v>
+      </c>
+      <c r="B123" s="6" t="s">
         <v>4293</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>4294</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
+        <v>4294</v>
+      </c>
+      <c r="B124" t="s">
         <v>4295</v>
-      </c>
-      <c r="B124" t="s">
-        <v>4296</v>
       </c>
       <c r="C124" s="6"/>
     </row>
     <row r="125" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
+        <v>4296</v>
+      </c>
+      <c r="B125" t="s">
         <v>4297</v>
-      </c>
-      <c r="B125" t="s">
-        <v>4298</v>
       </c>
       <c r="C125" s="6"/>
     </row>
     <row r="126" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
+        <v>4298</v>
+      </c>
+      <c r="B126" s="6" t="s">
         <v>4299</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>4300</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
+        <v>4300</v>
+      </c>
+      <c r="B127" s="6" t="s">
         <v>4301</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>4302</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
+        <v>4302</v>
+      </c>
+      <c r="B128" t="s">
         <v>4303</v>
-      </c>
-      <c r="B128" t="s">
-        <v>4304</v>
       </c>
       <c r="C128" s="6"/>
     </row>
     <row r="129" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>4305</v>
+        <v>4304</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>1491</v>
@@ -29391,15 +35499,15 @@
     </row>
     <row r="130" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
+        <v>4305</v>
+      </c>
+      <c r="B130" s="6" t="s">
         <v>4306</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>4307</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>4308</v>
+        <v>4307</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>1714</v>
@@ -29407,40 +35515,40 @@
     </row>
     <row r="132" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
+        <v>4308</v>
+      </c>
+      <c r="B132" s="6" t="s">
         <v>4309</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>4310</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
+        <v>4310</v>
+      </c>
+      <c r="B133" s="6" t="s">
         <v>4311</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>4312</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
+        <v>4312</v>
+      </c>
+      <c r="B134" t="s">
         <v>4313</v>
-      </c>
-      <c r="B134" t="s">
-        <v>4314</v>
       </c>
       <c r="C134" s="6"/>
     </row>
     <row r="135" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
+        <v>4314</v>
+      </c>
+      <c r="B135" s="6" t="s">
         <v>4315</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>4316</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>4317</v>
+        <v>4316</v>
       </c>
       <c r="B136" t="s">
         <v>3685</v>
@@ -29449,16 +35557,16 @@
     </row>
     <row r="137" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
+        <v>4317</v>
+      </c>
+      <c r="B137" t="s">
         <v>4318</v>
-      </c>
-      <c r="B137" t="s">
-        <v>4319</v>
       </c>
       <c r="C137" s="6"/>
     </row>
     <row r="138" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>4320</v>
+        <v>4319</v>
       </c>
       <c r="B138" t="s">
         <v>1376</v>
@@ -29467,16 +35575,16 @@
     </row>
     <row r="139" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
+        <v>4320</v>
+      </c>
+      <c r="B139" t="s">
         <v>4321</v>
-      </c>
-      <c r="B139" t="s">
-        <v>4322</v>
       </c>
       <c r="C139" s="6"/>
     </row>
     <row r="140" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>4323</v>
+        <v>4322</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>728</v>
@@ -29484,7 +35592,7 @@
     </row>
     <row r="141" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>4324</v>
+        <v>4323</v>
       </c>
       <c r="B141" t="s">
         <v>1156</v>
@@ -29493,7 +35601,7 @@
     </row>
     <row r="142" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>4325</v>
+        <v>4324</v>
       </c>
       <c r="B142" t="s">
         <v>1287</v>
@@ -29502,7 +35610,7 @@
     </row>
     <row r="143" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>4326</v>
+        <v>4325</v>
       </c>
       <c r="B143" t="s">
         <v>1726</v>
@@ -29511,16 +35619,16 @@
     </row>
     <row r="144" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
+        <v>4326</v>
+      </c>
+      <c r="B144" t="s">
         <v>4327</v>
-      </c>
-      <c r="B144" t="s">
-        <v>4328</v>
       </c>
       <c r="C144" s="6"/>
     </row>
     <row r="145" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
-        <v>4329</v>
+        <v>4328</v>
       </c>
       <c r="B145" t="s">
         <v>1533</v>
@@ -29529,7 +35637,7 @@
     </row>
     <row r="146" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>4330</v>
+        <v>4329</v>
       </c>
       <c r="B146" t="s">
         <v>726</v>
@@ -29538,40 +35646,40 @@
     </row>
     <row r="147" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
+        <v>4330</v>
+      </c>
+      <c r="B147" s="6" t="s">
         <v>4331</v>
-      </c>
-      <c r="B147" s="6" t="s">
-        <v>4332</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
+        <v>4332</v>
+      </c>
+      <c r="B148" s="6" t="s">
         <v>4333</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>4334</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>4335</v>
+        <v>4334</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>4398</v>
+        <v>4397</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
+        <v>4335</v>
+      </c>
+      <c r="B150" t="s">
         <v>4336</v>
-      </c>
-      <c r="B150" t="s">
-        <v>4337</v>
       </c>
       <c r="C150" s="6"/>
     </row>
     <row r="151" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>4338</v>
+        <v>4337</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>1701</v>
@@ -29579,15 +35687,15 @@
     </row>
     <row r="152" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
+        <v>4338</v>
+      </c>
+      <c r="B152" s="6" t="s">
         <v>4339</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>4340</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>4341</v>
+        <v>4340</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>1637</v>
@@ -29595,7 +35703,7 @@
     </row>
     <row r="154" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>4342</v>
+        <v>4341</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>1603</v>
@@ -29603,16 +35711,16 @@
     </row>
     <row r="155" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
+        <v>4342</v>
+      </c>
+      <c r="B155" t="s">
         <v>4343</v>
-      </c>
-      <c r="B155" t="s">
-        <v>4344</v>
       </c>
       <c r="C155" s="6"/>
     </row>
     <row r="156" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>4345</v>
+        <v>4344</v>
       </c>
       <c r="B156" t="s">
         <v>119</v>
@@ -29621,7 +35729,7 @@
     </row>
     <row r="157" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>4346</v>
+        <v>4345</v>
       </c>
       <c r="B157" t="s">
         <v>884</v>
@@ -29630,33 +35738,33 @@
     </row>
     <row r="158" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
+        <v>4346</v>
+      </c>
+      <c r="B158" t="s">
         <v>4347</v>
-      </c>
-      <c r="B158" t="s">
-        <v>4348</v>
       </c>
       <c r="C158" s="6"/>
     </row>
     <row r="159" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
+        <v>4348</v>
+      </c>
+      <c r="B159" t="s">
         <v>4349</v>
-      </c>
-      <c r="B159" t="s">
-        <v>4350</v>
       </c>
       <c r="C159" s="6"/>
     </row>
     <row r="160" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
+        <v>4350</v>
+      </c>
+      <c r="B160" s="6" t="s">
         <v>4351</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>4352</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>4353</v>
+        <v>4352</v>
       </c>
       <c r="B161" t="s">
         <v>1533</v>
@@ -29665,7 +35773,7 @@
     </row>
     <row r="162" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>4354</v>
+        <v>4353</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>1605</v>
@@ -29673,92 +35781,92 @@
     </row>
     <row r="163" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
+        <v>4354</v>
+      </c>
+      <c r="B163" s="6" t="s">
         <v>4355</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>4356</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
+        <v>4356</v>
+      </c>
+      <c r="B164" s="6" t="s">
         <v>4357</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>4358</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
+        <v>4358</v>
+      </c>
+      <c r="B165" t="s">
         <v>4359</v>
-      </c>
-      <c r="B165" t="s">
-        <v>4360</v>
       </c>
       <c r="C165" s="6"/>
     </row>
     <row r="166" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
+        <v>4360</v>
+      </c>
+      <c r="B166" s="6" t="s">
         <v>4361</v>
-      </c>
-      <c r="B166" s="6" t="s">
-        <v>4362</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
+        <v>4362</v>
+      </c>
+      <c r="B167" t="s">
         <v>4363</v>
-      </c>
-      <c r="B167" t="s">
-        <v>4364</v>
       </c>
       <c r="C167" s="6"/>
     </row>
     <row r="168" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
+        <v>4364</v>
+      </c>
+      <c r="B168" t="s">
         <v>4365</v>
-      </c>
-      <c r="B168" t="s">
-        <v>4366</v>
       </c>
       <c r="C168" s="6"/>
     </row>
     <row r="169" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
+        <v>4366</v>
+      </c>
+      <c r="B169" t="s">
         <v>4367</v>
-      </c>
-      <c r="B169" t="s">
-        <v>4368</v>
       </c>
       <c r="C169" s="6"/>
     </row>
     <row r="170" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
+        <v>4368</v>
+      </c>
+      <c r="B170" t="s">
         <v>4369</v>
-      </c>
-      <c r="B170" t="s">
-        <v>4370</v>
       </c>
       <c r="C170" s="6"/>
     </row>
     <row r="171" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
+        <v>4370</v>
+      </c>
+      <c r="B171" s="6" t="s">
         <v>4371</v>
-      </c>
-      <c r="B171" s="6" t="s">
-        <v>4372</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
+        <v>4372</v>
+      </c>
+      <c r="B172" s="6" t="s">
         <v>4373</v>
-      </c>
-      <c r="B172" s="6" t="s">
-        <v>4374</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
-        <v>4375</v>
+        <v>4374</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>110</v>
@@ -29766,52 +35874,52 @@
     </row>
     <row r="174" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
+        <v>4375</v>
+      </c>
+      <c r="B174" t="s">
         <v>4376</v>
-      </c>
-      <c r="B174" t="s">
-        <v>4377</v>
       </c>
       <c r="C174" s="6"/>
     </row>
     <row r="175" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
+        <v>4377</v>
+      </c>
+      <c r="B175" t="s">
         <v>4378</v>
-      </c>
-      <c r="B175" t="s">
-        <v>4379</v>
       </c>
       <c r="C175" s="6"/>
     </row>
     <row r="176" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
+        <v>4379</v>
+      </c>
+      <c r="B176" t="s">
         <v>4380</v>
-      </c>
-      <c r="B176" t="s">
-        <v>4381</v>
       </c>
       <c r="C176" s="6"/>
     </row>
     <row r="177" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
+        <v>4381</v>
+      </c>
+      <c r="B177" t="s">
         <v>4382</v>
-      </c>
-      <c r="B177" t="s">
-        <v>4383</v>
       </c>
       <c r="C177" s="6"/>
     </row>
     <row r="178" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
+        <v>4383</v>
+      </c>
+      <c r="B178" t="s">
         <v>4384</v>
-      </c>
-      <c r="B178" t="s">
-        <v>4385</v>
       </c>
       <c r="C178" s="6"/>
     </row>
     <row r="179" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
-        <v>4386</v>
+        <v>4385</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>3707</v>
@@ -29819,23 +35927,23 @@
     </row>
     <row r="180" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
+        <v>4386</v>
+      </c>
+      <c r="B180" s="6" t="s">
         <v>4387</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>4388</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
+        <v>4388</v>
+      </c>
+      <c r="B181" s="6" t="s">
         <v>4389</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>4390</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
-        <v>4391</v>
+        <v>4390</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>1150</v>
@@ -29843,26 +35951,29 @@
     </row>
     <row r="183" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
+        <v>4391</v>
+      </c>
+      <c r="B183" s="6" t="s">
         <v>4392</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>4393</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
+        <v>4393</v>
+      </c>
+      <c r="B184" s="6" t="s">
         <v>4394</v>
       </c>
-      <c r="B184" s="6" t="s">
-        <v>4395</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Syllabus!A1" display="এক কথায় প্রকাশ"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:B932"/>
@@ -37355,7 +43466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B348"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37364,11 +43475,11 @@
     <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>4876</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>1848</v>
       </c>
     </row>
@@ -40149,1829 +46260,9 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B144"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>2693</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2694</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>2695</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2696</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2697</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>2698</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>2699</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>2700</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>2701</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>2702</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>2703</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>2704</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>2705</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>2706</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>2707</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>2708</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>2709</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>2710</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>2711</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>2712</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>2713</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>2714</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>2715</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>2716</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>2717</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>2718</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>2719</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>2720</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>2721</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>2722</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>2723</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>2724</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>2725</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>2726</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>2727</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>2728</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>2729</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>2730</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>2731</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>2732</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>2733</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>2734</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>2735</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>2736</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>2737</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>2738</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>2739</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>2740</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>2741</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>2742</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>2743</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>2744</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>2745</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>2746</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>2747</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>2748</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>2749</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>2750</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>2751</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>2752</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>2753</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>2754</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>2755</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>2756</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>2757</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>2758</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>2759</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>2760</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>2761</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>2762</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>2763</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>2764</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>2765</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>2766</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>2767</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>2768</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>2769</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>2770</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>2771</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>2772</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>2773</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>2774</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>2775</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>2776</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>2777</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>2778</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>2779</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>2780</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>2781</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>2782</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>2783</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>2784</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>2785</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>2786</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>2787</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>2788</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>2789</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>2790</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>2791</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>2792</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>2793</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>2794</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>2795</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>2796</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>2797</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>2798</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>2799</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>2800</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>2801</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>2802</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>2803</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>2804</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>2805</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>1672</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>2806</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>2807</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>2808</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>2809</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>2810</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>2811</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>2812</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>2813</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>2814</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>2815</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>2816</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>2817</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>2818</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>2819</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>2820</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>2821</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>2822</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>2823</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>2824</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>2825</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>2827</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>2828</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>2829</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>2830</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>2831</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>2832</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>2833</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>2834</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>2835</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>2836</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>2837</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>2838</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>2839</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>2840</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>2841</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>2842</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>2844</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>2845</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>2846</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>2847</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>2848</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>2849</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>2850</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>2851</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>2852</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>2853</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>2854</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>2855</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>2856</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>2857</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>2858</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>2859</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>2860</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>2861</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>2862</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
-        <v>2863</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>2864</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
-        <v>2865</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>2866</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
-        <v>2867</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>2868</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>2870</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
-        <v>2871</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>2872</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
-        <v>2873</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>2874</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
-        <v>1813</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>2875</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
-        <v>2876</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>2877</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
-        <v>2878</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>2879</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
-        <v>2880</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>2881</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
-        <v>2882</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>2883</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
-        <v>2884</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>2885</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
-        <v>2886</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>2887</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
-        <v>2888</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>2889</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
-        <v>2890</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>2891</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
-        <v>2892</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>2893</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
-        <v>2894</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>2895</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
-        <v>2896</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>2897</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
-        <v>2898</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>2899</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
-        <v>2900</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>2901</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="s">
-        <v>2902</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>2903</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
-        <v>2904</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>2905</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
-        <v>2747</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>2748</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="3" t="s">
-        <v>2906</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>2907</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="3" t="s">
-        <v>2908</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>2909</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="s">
-        <v>2910</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>2911</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="s">
-        <v>2912</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>2913</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="3" t="s">
-        <v>2914</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>2915</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
-        <v>2916</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>2917</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
-        <v>2918</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>2919</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
-        <v>2920</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>2921</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
-        <v>2922</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>2923</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
-        <v>2924</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>2925</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
-        <v>2926</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>2927</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
-        <v>2928</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>2929</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="s">
-        <v>2930</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>2931</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
-        <v>2932</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>2933</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
-        <v>2934</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>2935</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
-        <v>2936</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>2937</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="3" t="s">
-        <v>2938</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>2939</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="s">
-        <v>2940</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>2941</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="s">
-        <v>2942</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>2943</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="s">
-        <v>2944</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>2945</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="3" t="s">
-        <v>2946</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>2947</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="s">
-        <v>2948</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>2949</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="s">
-        <v>2950</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>2951</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
-        <v>2952</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>2953</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="3" t="s">
-        <v>1537</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>2954</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="3" t="s">
-        <v>2955</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>2956</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="3" t="s">
-        <v>2957</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>2958</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="3" t="s">
-        <v>2959</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>2960</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="3" t="s">
-        <v>2961</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>2962</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="s">
-        <v>2963</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>2964</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="s">
-        <v>2965</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>2966</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="3" t="s">
-        <v>2967</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>2968</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="3" t="s">
-        <v>2969</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>2970</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B144"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B80"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1850</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1851</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1852</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1853</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1854</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1855</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1858</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1859</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1860</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>1862</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>1866</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1867</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1868</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1869</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1870</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1871</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>1872</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1873</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>1874</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>1876</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1877</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>1878</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>1880</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1881</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>1882</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>1884</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>1886</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>1888</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>1890</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1891</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1893</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>1894</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>1896</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1897</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>1898</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1899</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>1900</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1901</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>1902</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>1904</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1905</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>1906</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1907</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>1908</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1909</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>1910</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1911</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>1912</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1913</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>1914</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>1916</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1919</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>1922</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1923</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>1924</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1925</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>1926</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1927</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1931</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>1932</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1933</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>1934</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1935</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1937</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>1938</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1939</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>1940</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>1942</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>1944</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>1948</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>1950</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>1952</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>1954</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>1957</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>1959</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>1961</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1962</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>1963</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>1965</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1966</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>1967</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1968</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>1969</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>1971</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>1973</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>1975</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>1977</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1978</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>1979</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>1529</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>1982</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1983</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>1984</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1985</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1987</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>1988</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>1990</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>1994</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>1996</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>1998</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2000</v>
-      </c>
-      <c r="B78" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B79" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>2004</v>
-      </c>
-      <c r="B80" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B80"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Syllabus!A1" display="সন্ধি বিচ্ছেদ করো।"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>